--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -625,7 +625,7 @@
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Within 250 mi of 98101 · under 50k mi · under $29k list · clean title / no accidents · Prices captured Aug 7, 2026 — listings change daily; verify before contacting. OTD = list × 1.1035 + $750 (+ xfer); 6.30% APR / 60 mo.</t>
+          <t>Within 250 mi of 98101 · under 50k mi · under $29k list · clean title / no accidents · Prices captured Aug 7, 2026 — listings change daily; verify before contacting. OTD = list × 1.1105 + $800 (+ xfer) — 11.05% tax (2026 all-in Seattle vehicle rate) + $200 doc + $600 est. license/title/RTA; 6.30% APR / 60 mo.</t>
         </is>
       </c>
     </row>
@@ -780,16 +780,16 @@
         </is>
       </c>
       <c r="O6" s="10" t="n">
-        <v>31868</v>
+        <v>32115</v>
       </c>
       <c r="P6" s="10" t="n">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="Q6" s="10" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="R6" s="10" t="n">
-        <v>5365</v>
+        <v>5407</v>
       </c>
       <c r="S6" s="11" t="inlineStr">
         <is>
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="O7" s="10" t="n">
-        <v>30876</v>
+        <v>31117</v>
       </c>
       <c r="P7" s="10" t="n">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="Q7" s="10" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="R7" s="10" t="n">
-        <v>5198</v>
+        <v>5239</v>
       </c>
       <c r="S7" s="11" t="inlineStr">
         <is>
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="O8" s="10" t="n">
-        <v>28336</v>
+        <v>28561</v>
       </c>
       <c r="P8" s="10" t="n">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="Q8" s="10" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="R8" s="10" t="n">
-        <v>4771</v>
+        <v>4808</v>
       </c>
       <c r="S8" s="11" t="inlineStr">
         <is>
@@ -1008,16 +1008,16 @@
         </is>
       </c>
       <c r="O9" s="10" t="n">
-        <v>30006</v>
+        <v>30242</v>
       </c>
       <c r="P9" s="10" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="Q9" s="10" t="n">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="R9" s="10" t="n">
-        <v>5052</v>
+        <v>5091</v>
       </c>
       <c r="S9" s="11" t="inlineStr">
         <is>
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="O10" s="10" t="n">
-        <v>28549</v>
+        <v>28776</v>
       </c>
       <c r="P10" s="10" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="Q10" s="10" t="n">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="R10" s="10" t="n">
-        <v>4806</v>
+        <v>4845</v>
       </c>
       <c r="S10" s="11" t="inlineStr">
         <is>
@@ -1160,16 +1160,16 @@
         </is>
       </c>
       <c r="O11" s="10" t="n">
-        <v>28556</v>
+        <v>28782</v>
       </c>
       <c r="P11" s="10" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="Q11" s="10" t="n">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="R11" s="10" t="n">
-        <v>4808</v>
+        <v>4846</v>
       </c>
       <c r="S11" s="11" t="inlineStr">
         <is>
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="O12" s="10" t="n">
-        <v>30514</v>
+        <v>30752</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="Q12" s="10" t="n">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="R12" s="10" t="n">
-        <v>5137</v>
+        <v>5177</v>
       </c>
       <c r="S12" s="11" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         </is>
       </c>
       <c r="O13" s="10" t="n">
-        <v>30434</v>
+        <v>30672</v>
       </c>
       <c r="P13" s="10" t="n">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="Q13" s="10" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="R13" s="10" t="n">
-        <v>5124</v>
+        <v>5164</v>
       </c>
       <c r="S13" s="11" t="inlineStr">
         <is>
@@ -1388,16 +1388,16 @@
         </is>
       </c>
       <c r="O14" s="10" t="n">
-        <v>31316</v>
+        <v>31560</v>
       </c>
       <c r="P14" s="10" t="n">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="Q14" s="10" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="R14" s="10" t="n">
-        <v>5272</v>
+        <v>5313</v>
       </c>
       <c r="S14" s="11" t="inlineStr">
         <is>
@@ -1464,16 +1464,16 @@
         </is>
       </c>
       <c r="O15" s="10" t="n">
-        <v>27339</v>
+        <v>27557</v>
       </c>
       <c r="P15" s="10" t="n">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="Q15" s="10" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="R15" s="10" t="n">
-        <v>4603</v>
+        <v>4639</v>
       </c>
       <c r="S15" s="11" t="inlineStr">
         <is>
@@ -1540,16 +1540,16 @@
         </is>
       </c>
       <c r="O16" s="10" t="n">
-        <v>28534</v>
+        <v>28759</v>
       </c>
       <c r="P16" s="10" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="Q16" s="10" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="R16" s="10" t="n">
-        <v>4804</v>
+        <v>4842</v>
       </c>
       <c r="S16" s="11" t="inlineStr">
         <is>
@@ -1715,11 +1715,16 @@
     <row r="10">
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Seattle sales tax</t>
+          <t>Sales tax</t>
         </is>
       </c>
       <c r="C10" s="15" t="n">
-        <v>0.1035</v>
+        <v>0.1105</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>2026 all-in Seattle vehicle rate (10.55% combined + 0.5% WA motor-vehicle tax). WA-dealer sales are taxed at the dealer's city rate (10.4–11.2% around Puget Sound; Kirkland/Puyallup 10.80%); Oregon-dealer purchases owe 11.05% WA use tax at registration. Earlier versions used 10.35%.</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1731,15 +1736,25 @@
       <c r="C11" s="17" t="n">
         <v>200</v>
       </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>WA cap $200 (Oregon $250)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Title / registration</t>
+          <t>License / title / RTA (est.)</t>
         </is>
       </c>
       <c r="C12" s="17" t="n">
-        <v>550</v>
+        <v>600</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Year-one WA license, title, plates and Sound Transit RTA excise for a ~$26k 2021–23 CX-5 garaged in Seattle runs roughly $500–750; RTA is the big piece</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1750,7 +1765,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>OTD = list × (1 + tax) + doc + title/reg (+ transfer fee where noted)  →  list × 1.1035 + $750 at defaults</t>
+          <t>OTD = list × (1 + tax) + doc + license/title/RTA (+ transfer fee where noted)  →  list × 1.1105 + $800 at defaults</t>
         </is>
       </c>
     </row>
@@ -1885,16 +1900,16 @@
         <v/>
       </c>
       <c r="K18" s="24" t="n">
-        <v>31868</v>
+        <v>32115</v>
       </c>
       <c r="L18" s="24" t="n">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="M18" s="24" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="N18" s="24" t="n">
-        <v>5365</v>
+        <v>5407</v>
       </c>
     </row>
     <row r="19">
@@ -1933,16 +1948,16 @@
         <v/>
       </c>
       <c r="K19" s="24" t="n">
-        <v>30876</v>
+        <v>31117</v>
       </c>
       <c r="L19" s="24" t="n">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="M19" s="24" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="N19" s="24" t="n">
-        <v>5198</v>
+        <v>5239</v>
       </c>
     </row>
     <row r="20">
@@ -1981,16 +1996,16 @@
         <v/>
       </c>
       <c r="K20" s="24" t="n">
-        <v>28336</v>
+        <v>28561</v>
       </c>
       <c r="L20" s="24" t="n">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="M20" s="24" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="N20" s="24" t="n">
-        <v>4771</v>
+        <v>4808</v>
       </c>
     </row>
     <row r="21">
@@ -2029,16 +2044,16 @@
         <v/>
       </c>
       <c r="K21" s="24" t="n">
-        <v>30006</v>
+        <v>30242</v>
       </c>
       <c r="L21" s="24" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="M21" s="24" t="n">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="N21" s="24" t="n">
-        <v>5052</v>
+        <v>5091</v>
       </c>
     </row>
     <row r="22">
@@ -2077,16 +2092,16 @@
         <v/>
       </c>
       <c r="K22" s="24" t="n">
-        <v>28549</v>
+        <v>28776</v>
       </c>
       <c r="L22" s="24" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="M22" s="24" t="n">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="N22" s="24" t="n">
-        <v>4806</v>
+        <v>4845</v>
       </c>
     </row>
     <row r="23">
@@ -2125,16 +2140,16 @@
         <v/>
       </c>
       <c r="K23" s="24" t="n">
-        <v>28556</v>
+        <v>28782</v>
       </c>
       <c r="L23" s="24" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="M23" s="24" t="n">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="N23" s="24" t="n">
-        <v>4808</v>
+        <v>4846</v>
       </c>
     </row>
     <row r="24">
@@ -2173,16 +2188,16 @@
         <v/>
       </c>
       <c r="K24" s="24" t="n">
-        <v>30514</v>
+        <v>30752</v>
       </c>
       <c r="L24" s="24" t="n">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="M24" s="24" t="n">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="N24" s="24" t="n">
-        <v>5137</v>
+        <v>5177</v>
       </c>
     </row>
     <row r="25">
@@ -2221,16 +2236,16 @@
         <v/>
       </c>
       <c r="K25" s="24" t="n">
-        <v>30434</v>
+        <v>30672</v>
       </c>
       <c r="L25" s="24" t="n">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="M25" s="24" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="N25" s="24" t="n">
-        <v>5124</v>
+        <v>5164</v>
       </c>
     </row>
     <row r="26">
@@ -2269,16 +2284,16 @@
         <v/>
       </c>
       <c r="K26" s="24" t="n">
-        <v>31316</v>
+        <v>31560</v>
       </c>
       <c r="L26" s="24" t="n">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="M26" s="24" t="n">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="N26" s="24" t="n">
-        <v>5272</v>
+        <v>5313</v>
       </c>
     </row>
     <row r="27">
@@ -2317,16 +2332,16 @@
         <v/>
       </c>
       <c r="K27" s="24" t="n">
-        <v>27339</v>
+        <v>27557</v>
       </c>
       <c r="L27" s="24" t="n">
-        <v>532</v>
+        <v>537</v>
       </c>
       <c r="M27" s="24" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="N27" s="24" t="n">
-        <v>4603</v>
+        <v>4639</v>
       </c>
     </row>
     <row r="28">
@@ -2365,16 +2380,16 @@
         <v/>
       </c>
       <c r="K28" s="24" t="n">
-        <v>28534</v>
+        <v>28759</v>
       </c>
       <c r="L28" s="24" t="n">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="M28" s="24" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="N28" s="24" t="n">
-        <v>4804</v>
+        <v>4842</v>
       </c>
     </row>
     <row r="30">
@@ -2508,7 +2523,7 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>report: +$3,007 list, +$3,318 OTD, +$65/mo</t>
+          <t>report: +$3,007 list, +$3,339 OTD, +$65/mo</t>
         </is>
       </c>
     </row>
@@ -16218,7 +16233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F31"/>
+  <dimension ref="B2:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -16308,7 +16323,7 @@
       <c r="B11" s="18" t="inlineStr"/>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Cheapest solid vs. stretch: 2021 Grand Touring at $25,192 ($556/mo) vs. 2023 2.5 Turbo at $28,199 ($621/mo) — +$3,007 list, +$65/mo buys two model years, the turbo, and 5k fewer miles.</t>
+          <t>Cheapest solid vs. stretch: 2021 Grand Touring at $25,192 ($560/mo) vs. 2023 2.5 Turbo at $28,199 ($625/mo) — +$3,007 list, +$65/mo buys two model years, the turbo, and 5k fewer miles.</t>
         </is>
       </c>
     </row>
@@ -16336,51 +16351,55 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>OTD = list × (1 + 10.35% Seattle sales tax) + $200 doc + $550 title/registration = list × 1.1035 + $750 (+ CarMax transfer fee where noted)</t>
+          <t>OTD = list × (1 + 11.05% sales tax, 2026 all-in Seattle vehicle rate) + $200 doc + $600 est. license/title/RTA = list × 1.1105 + $800 (+ CarMax transfer fee where noted)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>Payment formula</t>
+          <t>Tax note</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>M = P · r(1+r)^n / ((1+r)^n − 1), r = APR/12, n = 60. APR 6.30% = Bankrate super-prime used-auto average (7/31/26); BECU 5.99% (8/1/26); no Mazda CPO promo on CX-5.</t>
+          <t>WA-dealer sales are taxed at the dealer's city rate (10.4–11.2% around Puget Sound in 2026), so a Kirkland or Puyallup dealer runs ~0.25 pt lower; Oregon-dealer purchases owe 11.05% WA use tax at registration. Earlier versions of this page used 10.35%, which understated OTD by roughly $200–250.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="18" t="inlineStr">
         <is>
+          <t>Payment formula</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>M = P · r(1+r)^n / ((1+r)^n − 1), r = APR/12, n = 60. APR 6.30% = Bankrate super-prime used-auto average (7/31/26); BECU 5.99% (8/1/26); no Mazda CPO promo on CX-5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
           <t>Rule of thumb</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Rule of thumb: every $1,000 financed ≈ $19.47/mo at 6.30% / 60 mo.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="18" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Filter rules</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Disqualify: any reported accident, fleet / rental prior use, lemon or frame-damage flag, fewer than 6 photos (where photo count is known), missing VIN (unless Craigslist / iSeeCars-flagged), missing price or miles.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="18" t="inlineStr"/>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Trim: unwanted trims (Sport, Select, base 2.5 S) dropped unless priced more than $3k under the year average.</t>
         </is>
       </c>
     </row>
@@ -16388,89 +16407,97 @@
       <c r="B21" s="18" t="inlineStr"/>
       <c r="C21" s="8" t="inlineStr">
         <is>
+          <t>Trim: unwanted trims (Sport, Select, base 2.5 S) dropped unless priced more than $3k under the year average.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="18" t="inlineStr"/>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
           <t>Rank: deal rating / KBB FPP delta → $ below market → 1-owner → CPO → miles per dollar; at least 3 non-CarGurus sources and all 3 model years enforced on the shortlist.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>Dedupe</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Dedupe: 278 raw → 153 unique VINs (VIN-matched) + 10 no-VIN orphans. 21 no-VIN records soft-matched to existing VINs by (year, ±1k mi, ±$250) and folded in as “also on” tags.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="18" t="inlineStr">
         <is>
+          <t>Dedupe</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Dedupe: 278 raw → 153 unique VINs (VIN-matched) + 10 no-VIN orphans. 21 no-VIN records soft-matched to existing VINs by (year, ±1k mi, ±$250) and folded in as “also on” tags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="18" t="inlineStr">
+        <is>
           <t>Recalls</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>NHTSA recalls: 0 open campaigns for MY2021–2023 CX-5 (checked 8/7/26). Verify by VIN at nhtsa.gov/recalls before purchase.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>Tabs</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Shortlist — the 11 picks with cost columns and links · Monthly cost — live calculator (edit blue cells) · Trim values — KBB FPP vs lowest clean listing · All listings — all 163 merged records with pass/fail and reason · No-haggle floor — CarMax/Carvana ceilings · Sources — coverage and method notes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="18" t="inlineStr">
         <is>
+          <t>Tabs</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Shortlist — the 11 picks with cost columns and links · Monthly cost — live calculator (edit blue cells) · Trim values — KBB FPP vs lowest clean listing · All listings — all 163 merged records with pass/fail and reason · No-haggle floor — CarMax/Carvana ceilings · Sources — coverage and method notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
           <t>Cell colors</t>
         </is>
       </c>
-      <c r="C26" s="8" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Blue = hardcoded value captured from a listing source or the published report; black = computed by formula; pale-yellow boxed cells are the inputs to change; gray = as-published reference values.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="90" customHeight="1">
-      <c r="B28" s="18" t="inlineStr">
+    <row r="29" ht="90" customHeight="1">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>Email template</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Hi — I'm Evan, looking at your [YEAR] Mazda CX-5 [TRIM], stock #[STOCK] / VIN [VIN]. I'm comparing several CX-5s in the Seattle area this week and narrowing to two or three. Could you email me an itemized out-the-door quote in writing — vehicle price, doc fee, sales tax, title/registration, and any dealer add-ons listed separately? I'm undecided on financing vs. outside lender, so please quote the cash OTD; we can talk financing after. Thanks — happy to come see the car once I have the numbers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>Disclaimer</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Research compiled Aug 7, 2026. Read-only scan — no dealer was contacted, no forms submitted. Not affiliated with any seller. Verify history reports and pricing independently before purchase.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="18" t="inlineStr">
         <is>
+          <t>Disclaimer</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Research compiled Aug 7, 2026. Read-only scan — no dealer was contacted, no forms submitted. Not affiliated with any seller. Verify history reports and pricing independently before purchase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="18" t="inlineStr">
+        <is>
           <t>Note on links</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Listing URLs were captured Aug 7, 2026 and may expire as cars sell. Pick #11 links to CarMax stock 70056694 (the 2022 Carbon Edition, 48,337 mi, Sacramento South) per the captured CarMax data.</t>
         </is>

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -132,13 +132,13 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -573,7 +573,7 @@
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Cheapest solid = lowest out-the-door figure (written quote where one exists, else the estimate) among live cars with a verified 1-owner / 0-accident history (or Mazda CPO) at a franchise dealer. Stretch = best-value live 2023 in the Turbo / Premium tiers, ranked by list price against KBB Seattle fair purchase price.</t>
+          <t>Cheapest solid = lowest estimated out-the-door figure among live cars with a verified 1-owner / 0-accident history (or Mazda CPO) at a franchise dealer. Stretch = best-value live 2023 in the Turbo / Premium tiers, ranked by list price against KBB Seattle fair purchase price.</t>
         </is>
       </c>
     </row>
@@ -615,7 +615,7 @@
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: $31,957.24 OTD, clean ($0 add-ons, $200 doc; tax + licence lumped).</t>
+          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>quote in preparation (Aug 11, 3:57 PM); Evan's $28,500 OTD counter sent. Oregon: email-only leverage.</t>
+          <t>quote in preparation (Aug 11, 3:57 PM); our written-number request is with the dealer. Oregon: email-only leverage.</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>written quote Aug 11, 4:21 PM: $24,992 selling / $28,591.14 OTD, zero add-ons; accept + deposit-hold reply staged. KBB lists the dealer as “Ford of Kirkland”; same lot.</t>
+          <t>written itemized quote received Aug 11, 4:21 PM (zero add-ons, doc fee at the state cap); reply prepared. KBB lists the dealer as “Ford of Kirkland”; same lot.</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>written quote received Aug 11 (PDF, figures not yet transcribed; it lists Courtesy Guard + Forever Start add-ons); Evan countered $29,600 OTD. Oregon: email-only.</t>
+          <t>written quote received Aug 11 as a PDF; it lists Courtesy Guard + Forever Start add-ons and their removal has been requested. Oregon: email-only.</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>revised written quote Aug 11, 4:43 PM: $31,000 OTD with the $995 KARR add-on struck (first sheet was $32,229.17); Evan holding at $30,200 OTD.</t>
+          <t>revised written quote received Aug 11, 4:43 PM with the KARR add-on struck; discussion ongoing.</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>written quote Aug 11: $31,957.24 OTD (clean sheet: $28,287 + $200 doc, $0 add-ons, tax + licence lumped at $3,470.24, not itemized); Evan countered $31,100 OTD; next ask is the itemized tax/licence.</t>
+          <t>written quote received Aug 11 (clean sheet; tax and licence lumped in one line, itemization requested); discussion ongoing.</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2135,7 +2135,7 @@
       <c r="W16" s="6" t="n"/>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>written $28,718.60 OTD ($25,400 selling, $0 doc, no add-ons) valid to Aug 12, 7 PM; Evan's $27,000 + inspection counter was declined.</t>
+          <t>written offer in hand, valid to Aug 12, 7 PM; Carfax shows a 6/2024 accident. Discussion paused.</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -2321,7 +2321,7 @@
       <c r="W18" s="6" t="n"/>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>folded into the #8 thread with a $29,400 OTD counter (Aug 11); no separate quote yet. Oregon: email-only.</t>
+          <t>folded into the #8 thread; no separate quote yet. Oregon: email-only.</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -2442,7 +2442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:T8"/>
+  <dimension ref="B1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -2584,335 +2584,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>2021 Grand Touring AWD</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Hyundai of Kirkland / Ford of Kirkland</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Aug 11 4:21 PM PT</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>itemized written proposal (email)</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="n">
-        <v>24992</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I4" s="11" t="n">
-        <v>2699.14</v>
-      </c>
-      <c r="J4" s="10" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>700</v>
-      </c>
-      <c r="L4" s="11" t="n"/>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="n">
-        <v>28591.14</v>
-      </c>
-      <c r="O4" s="11" t="n"/>
-      <c r="P4" s="12" t="n">
-        <v>28712.736</v>
-      </c>
-      <c r="Q4" s="9" t="n">
-        <v>27700</v>
-      </c>
-      <c r="R4" s="12">
-        <f>N4-Q4</f>
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>selling $200 under list; zero add-ons · counter: front-runner bump via site form; superseded by the priority rule: accept any clean sheet at or under list</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>2023 2.5 S Preferred</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Royal Moore Mazda</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Aug 11 3:06 PM PT</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>pricing breakdown PDF (figures not yet transcribed)</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="10" t="n"/>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="11" t="n"/>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>Courtesy Guard, Forever Start</t>
-        </is>
-      </c>
-      <c r="N5" s="11" t="n"/>
-      <c r="O5" s="11" t="n"/>
-      <c r="P5" s="12" t="n">
-        <v>30472.45</v>
-      </c>
-      <c r="Q5" s="9" t="n">
-        <v>29600</v>
-      </c>
-      <c r="R5" s="12" t="n"/>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>carries two dealer add-ons to strike · counter: two-car counter with #20 ($29,400)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>2022 2.5 S Premium Plus</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Titus-Will Chevrolet GMC Cadillac</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Aug 11 4:43 PM PT</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>revised written proposal (PDF)</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>27268.6</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="9" t="n">
-        <v>750</v>
-      </c>
-      <c r="L6" s="11" t="n"/>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="n">
-        <v>31000</v>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>32229.17</v>
-      </c>
-      <c r="P6" s="12" t="n">
-        <v>30982.678</v>
-      </c>
-      <c r="Q6" s="9" t="n">
-        <v>30200</v>
-      </c>
-      <c r="R6" s="12">
-        <f>N6-Q6</f>
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>$995 KARR add-on struck on the revision; $750 government fees to be trued up at actuals · counter: KARR + gov-fee strikes; holding</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>2023 2.5 S Premium</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Rodland Toyota of Everett</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>Aug 11 3:24 PM PT</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>'Estimated Pricing Summary' payment-estimator printout (PDF, 3 pages; not a signed buyer's order)</t>
-        </is>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>28487</v>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I7" s="11" t="n"/>
-      <c r="J7" s="10" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="11" t="n">
-        <v>3470.24</v>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>31957.24</v>
-      </c>
-      <c r="O7" s="11" t="n"/>
-      <c r="P7" s="12" t="n">
-        <v>32028.848</v>
-      </c>
-      <c r="Q7" s="9" t="n">
-        <v>31100</v>
-      </c>
-      <c r="R7" s="12">
-        <f>N7-Q7</f>
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>tax + licence lumped, consistent with Everett 10.40% plus ~$508 of title/licence; ask for the itemized rate and licence · counter: $27,300 selling; gap $857</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>2021 Grand Touring w/ GT Premium pkg</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Auto 206 (independent)</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Aug 11 1:57 PM PT</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>itemized written offer (email + PDF)</t>
-        </is>
-      </c>
-      <c r="G8" s="11" t="n">
-        <v>25400</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="11" t="n">
-        <v>2768.6</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="K8" s="9" t="n">
-        <v>550</v>
-      </c>
-      <c r="L8" s="11" t="n"/>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>28718.6</v>
-      </c>
-      <c r="O8" s="11" t="n"/>
-      <c r="P8" s="12" t="n">
-        <v>29211.091</v>
-      </c>
-      <c r="Q8" s="9" t="n">
-        <v>27000</v>
-      </c>
-      <c r="R8" s="12">
-        <f>N8-Q8</f>
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>cleanest fee sheet seen: no doc fee, no add-ons; disqualified by the Carfax accident unless the rule is waived · counter: contingent on a clean independent PPI; declined by the dealer</t>
-        </is>
-      </c>
-    </row>
+    <row r="4"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2971,7 +2643,7 @@
           <t>APR</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="11" t="n">
         <v>0.063</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -2979,7 +2651,7 @@
           <t>Per $1,000 financed</t>
         </is>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="12">
         <f>-PMT($C$3/12,$C$4,1000)</f>
         <v/>
       </c>
@@ -2990,10 +2662,10 @@
           <t>Term (months)</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="E4" s="16" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>Bankrate super-prime used-auto average, updated 7/31/26; credit-union check BECU 5.99% effective 8/1/26</t>
         </is>
@@ -3005,7 +2677,7 @@
           <t>Down payment (scenario 2)</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="15" t="n">
         <v>5000</v>
       </c>
     </row>
@@ -3015,7 +2687,7 @@
           <t>License / title / RTA est.</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="15" t="n">
         <v>600</v>
       </c>
     </row>
@@ -3119,24 +2791,24 @@
       <c r="H9" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="16">
         <f>F9*(1+G9)+H9+$C$6</f>
         <v/>
       </c>
-      <c r="J9" s="11" t="n"/>
-      <c r="K9" s="14">
+      <c r="J9" s="17" t="n"/>
+      <c r="K9" s="12">
         <f>IF(J9&gt;0,J9,I9)</f>
         <v/>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="16">
         <f>-PMT($C$3/12,$C$4,K9)</f>
         <v/>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K9-$C$5))</f>
         <v/>
       </c>
-      <c r="N9" s="12">
+      <c r="N9" s="16">
         <f>L9*$C$4-K9</f>
         <v/>
       </c>
@@ -3174,24 +2846,24 @@
       <c r="H10" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="16">
         <f>F10*(1+G10)+H10+$C$6</f>
         <v/>
       </c>
-      <c r="J10" s="11" t="n"/>
-      <c r="K10" s="14">
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="12">
         <f>IF(J10&gt;0,J10,I10)</f>
         <v/>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="16">
         <f>-PMT($C$3/12,$C$4,K10)</f>
         <v/>
       </c>
-      <c r="M10" s="12">
+      <c r="M10" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K10-$C$5))</f>
         <v/>
       </c>
-      <c r="N10" s="12">
+      <c r="N10" s="16">
         <f>L10*$C$4-K10</f>
         <v/>
       </c>
@@ -3217,7 +2889,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>est</t>
         </is>
       </c>
       <c r="F11" s="9" t="n">
@@ -3229,104 +2901,100 @@
       <c r="H11" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="16">
         <f>F11*(1+G11)+H11+$C$6</f>
         <v/>
       </c>
-      <c r="J11" s="11" t="n">
-        <v>28591.14</v>
-      </c>
-      <c r="K11" s="14">
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="12">
         <f>IF(J11&gt;0,J11,I11)</f>
         <v/>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="16">
         <f>-PMT($C$3/12,$C$4,K11)</f>
         <v/>
       </c>
-      <c r="M11" s="12">
+      <c r="M11" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K11-$C$5))</f>
         <v/>
       </c>
-      <c r="N11" s="12">
+      <c r="N11" s="16">
         <f>L11*$C$4-K11</f>
         <v/>
       </c>
       <c r="O11" s="7" t="inlineStr">
         <is>
-          <t>Aug 11 sheet</t>
+          <t>est. at Kirkland, WA rate</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>2021 Grand Touring w/ GT Premium pkg</t>
+          <t>2021 Signature (2.5T)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Auto 206 (independent)</t>
+          <t>Cortes Auto Center (independent)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>est</t>
         </is>
       </c>
       <c r="F12" s="9" t="n">
-        <v>25799</v>
+        <v>25999</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.109</v>
+        <v>0.091</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="12">
+        <v>200</v>
+      </c>
+      <c r="I12" s="16">
         <f>F12*(1+G12)+H12+$C$6</f>
         <v/>
       </c>
-      <c r="J12" s="11" t="n">
-        <v>28718.6</v>
-      </c>
-      <c r="K12" s="14">
+      <c r="J12" s="17" t="n"/>
+      <c r="K12" s="12">
         <f>IF(J12&gt;0,J12,I12)</f>
         <v/>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="16">
         <f>-PMT($C$3/12,$C$4,K12)</f>
         <v/>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K12-$C$5))</f>
         <v/>
       </c>
-      <c r="N12" s="12">
+      <c r="N12" s="16">
         <f>L12*$C$4-K12</f>
         <v/>
       </c>
       <c r="O12" s="7" t="inlineStr">
         <is>
-          <t>Aug 11 sheet</t>
+          <t>est. at Burlington, WA rate</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>2021 Signature (2.5T)</t>
+          <t>2021 Grand Touring w/ GT Premium pkg</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Cortes Auto Center (independent)</t>
+          <t>Auto 206 (independent)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -3335,38 +3003,38 @@
         </is>
       </c>
       <c r="F13" s="9" t="n">
-        <v>25999</v>
+        <v>25799</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0.091</v>
+        <v>0.109</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I13" s="12">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16">
         <f>F13*(1+G13)+H13+$C$6</f>
         <v/>
       </c>
-      <c r="J13" s="11" t="n"/>
-      <c r="K13" s="14">
+      <c r="J13" s="17" t="n"/>
+      <c r="K13" s="12">
         <f>IF(J13&gt;0,J13,I13)</f>
         <v/>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="16">
         <f>-PMT($C$3/12,$C$4,K13)</f>
         <v/>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K13-$C$5))</f>
         <v/>
       </c>
-      <c r="N13" s="12">
+      <c r="N13" s="16">
         <f>L13*$C$4-K13</f>
         <v/>
       </c>
       <c r="O13" s="7" t="inlineStr">
         <is>
-          <t>est. at Burlington, WA rate</t>
+          <t>est. at Kent, WA rate</t>
         </is>
       </c>
     </row>
@@ -3398,24 +3066,24 @@
       <c r="H14" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="16">
         <f>F14*(1+G14)+H14+$C$6</f>
         <v/>
       </c>
-      <c r="J14" s="11" t="n"/>
-      <c r="K14" s="14">
+      <c r="J14" s="17" t="n"/>
+      <c r="K14" s="12">
         <f>IF(J14&gt;0,J14,I14)</f>
         <v/>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="16">
         <f>-PMT($C$3/12,$C$4,K14)</f>
         <v/>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K14-$C$5))</f>
         <v/>
       </c>
-      <c r="N14" s="12">
+      <c r="N14" s="16">
         <f>L14*$C$4-K14</f>
         <v/>
       </c>
@@ -3453,24 +3121,24 @@
       <c r="H15" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="16">
         <f>F15*(1+G15)+H15+$C$6</f>
         <v/>
       </c>
-      <c r="J15" s="11" t="n"/>
-      <c r="K15" s="14">
+      <c r="J15" s="17" t="n"/>
+      <c r="K15" s="12">
         <f>IF(J15&gt;0,J15,I15)</f>
         <v/>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="16">
         <f>-PMT($C$3/12,$C$4,K15)</f>
         <v/>
       </c>
-      <c r="M15" s="12">
+      <c r="M15" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K15-$C$5))</f>
         <v/>
       </c>
-      <c r="N15" s="12">
+      <c r="N15" s="16">
         <f>L15*$C$4-K15</f>
         <v/>
       </c>
@@ -3508,24 +3176,24 @@
       <c r="H16" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="16">
         <f>F16*(1+G16)+H16+$C$6</f>
         <v/>
       </c>
-      <c r="J16" s="11" t="n"/>
-      <c r="K16" s="14">
+      <c r="J16" s="17" t="n"/>
+      <c r="K16" s="12">
         <f>IF(J16&gt;0,J16,I16)</f>
         <v/>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="16">
         <f>-PMT($C$3/12,$C$4,K16)</f>
         <v/>
       </c>
-      <c r="M16" s="12">
+      <c r="M16" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K16-$C$5))</f>
         <v/>
       </c>
-      <c r="N16" s="12">
+      <c r="N16" s="16">
         <f>L16*$C$4-K16</f>
         <v/>
       </c>
@@ -3563,24 +3231,24 @@
       <c r="H17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="16">
         <f>F17*(1+G17)+H17+$C$6</f>
         <v/>
       </c>
-      <c r="J17" s="11" t="n"/>
-      <c r="K17" s="14">
+      <c r="J17" s="17" t="n"/>
+      <c r="K17" s="12">
         <f>IF(J17&gt;0,J17,I17)</f>
         <v/>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="16">
         <f>-PMT($C$3/12,$C$4,K17)</f>
         <v/>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K17-$C$5))</f>
         <v/>
       </c>
-      <c r="N17" s="12">
+      <c r="N17" s="16">
         <f>L17*$C$4-K17</f>
         <v/>
       </c>
@@ -3618,24 +3286,24 @@
       <c r="H18" s="9" t="n">
         <v>250</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="16">
         <f>F18*(1+G18)+H18+$C$6</f>
         <v/>
       </c>
-      <c r="J18" s="11" t="n"/>
-      <c r="K18" s="14">
+      <c r="J18" s="17" t="n"/>
+      <c r="K18" s="12">
         <f>IF(J18&gt;0,J18,I18)</f>
         <v/>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="16">
         <f>-PMT($C$3/12,$C$4,K18)</f>
         <v/>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K18-$C$5))</f>
         <v/>
       </c>
-      <c r="N18" s="12">
+      <c r="N18" s="16">
         <f>L18*$C$4-K18</f>
         <v/>
       </c>
@@ -3661,7 +3329,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>est</t>
         </is>
       </c>
       <c r="F19" s="9" t="n">
@@ -3673,32 +3341,30 @@
       <c r="H19" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="16">
         <f>F19*(1+G19)+H19+$C$6</f>
         <v/>
       </c>
-      <c r="J19" s="11" t="n">
-        <v>31000</v>
-      </c>
-      <c r="K19" s="14">
+      <c r="J19" s="17" t="n"/>
+      <c r="K19" s="12">
         <f>IF(J19&gt;0,J19,I19)</f>
         <v/>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="16">
         <f>-PMT($C$3/12,$C$4,K19)</f>
         <v/>
       </c>
-      <c r="M19" s="12">
+      <c r="M19" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K19-$C$5))</f>
         <v/>
       </c>
-      <c r="N19" s="12">
+      <c r="N19" s="16">
         <f>L19*$C$4-K19</f>
         <v/>
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>Aug 11 sheet</t>
+          <t>est. at Olympia, WA rate</t>
         </is>
       </c>
     </row>
@@ -3730,24 +3396,24 @@
       <c r="H20" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="16">
         <f>F20*(1+G20)+H20+$C$6</f>
         <v/>
       </c>
-      <c r="J20" s="11" t="n"/>
-      <c r="K20" s="14">
+      <c r="J20" s="17" t="n"/>
+      <c r="K20" s="12">
         <f>IF(J20&gt;0,J20,I20)</f>
         <v/>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="16">
         <f>-PMT($C$3/12,$C$4,K20)</f>
         <v/>
       </c>
-      <c r="M20" s="12">
+      <c r="M20" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K20-$C$5))</f>
         <v/>
       </c>
-      <c r="N20" s="12">
+      <c r="N20" s="16">
         <f>L20*$C$4-K20</f>
         <v/>
       </c>
@@ -3785,24 +3451,24 @@
       <c r="H21" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="16">
         <f>F21*(1+G21)+H21+$C$6</f>
         <v/>
       </c>
-      <c r="J21" s="11" t="n"/>
-      <c r="K21" s="14">
+      <c r="J21" s="17" t="n"/>
+      <c r="K21" s="12">
         <f>IF(J21&gt;0,J21,I21)</f>
         <v/>
       </c>
-      <c r="L21" s="12">
+      <c r="L21" s="16">
         <f>-PMT($C$3/12,$C$4,K21)</f>
         <v/>
       </c>
-      <c r="M21" s="12">
+      <c r="M21" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K21-$C$5))</f>
         <v/>
       </c>
-      <c r="N21" s="12">
+      <c r="N21" s="16">
         <f>L21*$C$4-K21</f>
         <v/>
       </c>
@@ -3840,24 +3506,24 @@
       <c r="H22" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="16">
         <f>F22*(1+G22)+H22+$C$6</f>
         <v/>
       </c>
-      <c r="J22" s="11" t="n"/>
-      <c r="K22" s="14">
+      <c r="J22" s="17" t="n"/>
+      <c r="K22" s="12">
         <f>IF(J22&gt;0,J22,I22)</f>
         <v/>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="16">
         <f>-PMT($C$3/12,$C$4,K22)</f>
         <v/>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K22-$C$5))</f>
         <v/>
       </c>
-      <c r="N22" s="12">
+      <c r="N22" s="16">
         <f>L22*$C$4-K22</f>
         <v/>
       </c>
@@ -3938,7 +3604,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>quoted</t>
+          <t>est</t>
         </is>
       </c>
       <c r="F24" s="9" t="n">
@@ -3950,32 +3616,30 @@
       <c r="H24" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="16">
         <f>F24*(1+G24)+H24+$C$6</f>
         <v/>
       </c>
-      <c r="J24" s="11" t="n">
-        <v>31957.24</v>
-      </c>
-      <c r="K24" s="14">
+      <c r="J24" s="17" t="n"/>
+      <c r="K24" s="12">
         <f>IF(J24&gt;0,J24,I24)</f>
         <v/>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="16">
         <f>-PMT($C$3/12,$C$4,K24)</f>
         <v/>
       </c>
-      <c r="M24" s="12">
+      <c r="M24" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K24-$C$5))</f>
         <v/>
       </c>
-      <c r="N24" s="12">
+      <c r="N24" s="16">
         <f>L24*$C$4-K24</f>
         <v/>
       </c>
       <c r="O24" s="7" t="inlineStr">
         <is>
-          <t>Aug 11 sheet</t>
+          <t>est. at Everett, WA rate</t>
         </is>
       </c>
     </row>
@@ -4000,27 +3664,27 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>quoted</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="n">
-        <v>24992</v>
+          <t>est</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>25192</v>
       </c>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n"/>
-      <c r="K27" s="12" t="n">
-        <v>28591.14</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>556.7439727314284</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>459.3809482540154</v>
-      </c>
-      <c r="N27" s="12" t="n">
-        <v>4813.498363885701</v>
+      <c r="K27" s="16" t="n">
+        <v>28712.736</v>
+      </c>
+      <c r="L27" s="16" t="n">
+        <v>559.1117635962995</v>
+      </c>
+      <c r="M27" s="16" t="n">
+        <v>461.7487391188865</v>
+      </c>
+      <c r="N27" s="16" t="n">
+        <v>4833.969815777968</v>
       </c>
     </row>
     <row r="28">
@@ -4040,23 +3704,23 @@
           <t>est</t>
         </is>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="16" t="n">
         <v>27999</v>
       </c>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="7" t="n"/>
-      <c r="K28" s="12" t="n">
+      <c r="K28" s="16" t="n">
         <v>31822.892</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="L28" s="16" t="n">
         <v>619.6746025476141</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="M28" s="16" t="n">
         <v>522.3115780702011</v>
       </c>
-      <c r="N28" s="12" t="n">
+      <c r="N28" s="16" t="n">
         <v>5357.584152856845</v>
       </c>
     </row>
@@ -4070,29 +3734,29 @@
       <c r="D29" s="25" t="n"/>
       <c r="E29" s="25" t="n"/>
       <c r="F29" s="26" t="n">
-        <v>3007</v>
+        <v>2807</v>
       </c>
       <c r="G29" s="25" t="n"/>
       <c r="H29" s="25" t="n"/>
       <c r="I29" s="25" t="n"/>
       <c r="J29" s="25" t="n"/>
       <c r="K29" s="26" t="n">
-        <v>3231.752000000004</v>
+        <v>3110.156000000003</v>
       </c>
       <c r="L29" s="26" t="n">
-        <v>62.93062981618573</v>
+        <v>60.56283895131457</v>
       </c>
       <c r="M29" s="26" t="n">
-        <v>62.93062981618573</v>
+        <v>60.56283895131463</v>
       </c>
       <c r="N29" s="26" t="n">
-        <v>544.0857889711442</v>
+        <v>523.6143370788777</v>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>Rule: cheapest solid = lowest out-the-door figure (written quote where one exists, else the estimate) among live cars with a verified 1-owner / 0-accident history (or Mazda CPO) at a franchise dealer; stretch = best-value live 2023 in the Turbo / Premium tiers, ranked by list price against KBB Seattle fair purchase price.</t>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Rule: cheapest solid = lowest estimated out-the-door figure among live cars with a verified 1-owner / 0-accident history (or Mazda CPO) at a franchise dealer; stretch = best-value live 2023 in the Turbo / Premium tiers, ranked by list price against KBB Seattle fair purchase price.</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4202,7 @@
       <c r="F4" s="9" t="n">
         <v>27198</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="16" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
@@ -4582,7 +4246,7 @@
       <c r="F5" s="9" t="n">
         <v>24081</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="16" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="6" t="n"/>
@@ -4620,7 +4284,7 @@
       <c r="F6" s="9" t="n">
         <v>27260</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="16" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
@@ -4664,7 +4328,7 @@
       <c r="F7" s="9" t="n">
         <v>28998</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="16" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -4702,7 +4366,7 @@
       <c r="F8" s="9" t="n">
         <v>25895</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="16" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="6" t="n">
@@ -4746,7 +4410,7 @@
       <c r="F9" s="9" t="n">
         <v>25195</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="16" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="6" t="n">
@@ -4790,7 +4454,7 @@
       <c r="F10" s="9" t="n">
         <v>27999</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="16" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -4828,7 +4492,7 @@
       <c r="F11" s="9" t="n">
         <v>27722</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="16" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="6" t="n"/>
@@ -4864,7 +4528,7 @@
       <c r="F12" s="9" t="n">
         <v>27400</v>
       </c>
-      <c r="G12" s="12" t="n"/>
+      <c r="G12" s="16" t="n"/>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="3" t="inlineStr">
@@ -4900,7 +4564,7 @@
       <c r="F13" s="9" t="n">
         <v>25950</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="16" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="6" t="n"/>
@@ -5033,7 +4697,7 @@
           <t>CarMax</t>
         </is>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="16">
         <f>F4-IF(E4&gt;0,E4,D4)</f>
         <v/>
       </c>
@@ -5065,7 +4729,7 @@
           <t>CarMax</t>
         </is>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="16">
         <f>F5-IF(E5&gt;0,E5,D5)</f>
         <v/>
       </c>
@@ -5091,7 +4755,7 @@
       </c>
       <c r="F6" s="9" t="n"/>
       <c r="G6" s="7" t="n"/>
-      <c r="H6" s="12" t="n"/>
+      <c r="H6" s="16" t="n"/>
       <c r="I6" s="7" t="inlineStr"/>
       <c r="J6" s="6" t="n">
         <v>0</v>
@@ -5118,7 +4782,7 @@
           <t>#6</t>
         </is>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="16">
         <f>F7-IF(E7&gt;0,E7,D7)</f>
         <v/>
       </c>
@@ -5154,7 +4818,7 @@
           <t>CarMax</t>
         </is>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="16">
         <f>F8-IF(E8&gt;0,E8,D8)</f>
         <v/>
       </c>
@@ -5186,7 +4850,7 @@
           <t>#21</t>
         </is>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="16">
         <f>F9-IF(E9&gt;0,E9,D9)</f>
         <v/>
       </c>
@@ -5216,7 +4880,7 @@
           <t>CarGurus</t>
         </is>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="16">
         <f>F10-IF(E10&gt;0,E10,D10)</f>
         <v/>
       </c>
@@ -5250,7 +4914,7 @@
           <t>CarMax</t>
         </is>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="16">
         <f>F11-IF(E11&gt;0,E11,D11)</f>
         <v/>
       </c>
@@ -5286,7 +4950,7 @@
           <t>CarMax</t>
         </is>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="16">
         <f>F12-IF(E12&gt;0,E12,D12)</f>
         <v/>
       </c>
@@ -5318,7 +4982,7 @@
           <t>CarMax</t>
         </is>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="16">
         <f>F13-IF(E13&gt;0,E13,D13)</f>
         <v/>
       </c>
@@ -5350,7 +5014,7 @@
           <t>CarMax</t>
         </is>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="16">
         <f>F14-IF(E14&gt;0,E14,D14)</f>
         <v/>
       </c>
@@ -5380,7 +5044,7 @@
           <t>#10</t>
         </is>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="16">
         <f>F15-IF(E15&gt;0,E15,D15)</f>
         <v/>
       </c>
@@ -5416,7 +5080,7 @@
           <t>CarMax</t>
         </is>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="16">
         <f>F16-IF(E16&gt;0,E16,D16)</f>
         <v/>
       </c>
@@ -5448,7 +5112,7 @@
           <t>CarGurus</t>
         </is>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="16">
         <f>F17-IF(E17&gt;0,E17,D17)</f>
         <v/>
       </c>
@@ -5480,7 +5144,7 @@
           <t>CarMax</t>
         </is>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="16">
         <f>F18-IF(E18&gt;0,E18,D18)</f>
         <v/>
       </c>
@@ -5512,7 +5176,7 @@
           <t>#1</t>
         </is>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="16">
         <f>F19-IF(E19&gt;0,E19,D19)</f>
         <v/>
       </c>
@@ -5522,14 +5186,14 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>¹ Seattle FPP = mean of per-listing kbbFppAmount from KBB search results (n=1–5 per cell).</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>² No Seattle FPP for this cell; Δ shown vs national — national is systematically ~$3–5k low (default-zip, higher-mileage assumption), so treat these as “at market,” not overpriced.</t>
         </is>

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -116,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,6 +148,9 @@
     <xf numFmtId="167" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -515,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O19"/>
+  <dimension ref="B1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -629,26 +632,33 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
+          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
+          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Aug 7, 2026: Initial read-only market scan: 278 raw listings → 153 unique VINs → 112 pass the disqualifiers; 11-car shortlist ranked by value.</t>
         </is>
@@ -4092,26 +4102,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O13"/>
+  <dimension ref="B1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
+    <col width="55" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Screened and parked (re-checked Aug 12, 2026)</t>
+          <t>Watchlist: screened, not on the board (re-checked Aug 12, 2026)</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
@@ -4131,452 +4146,814 @@
     <row r="3">
       <c r="B3" s="5" t="inlineStr">
         <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
           <t>Car</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Dealer</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Price now</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Was</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Move</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>Days listed</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Deal</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>Why parked</t>
-        </is>
-      </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
+          <t>VIN</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>Est. OTD</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>/mo @ $0 dn</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Why parked / watch-only</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
           <t>URL</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>2022 2.5 S Carbon Edition, 47,333 mi, $26,998+$200</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Doug's Lynnwood Mazda</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>WA</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>27198</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>27198</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="I4" s="7" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Fair Deal rating, 47k mi; #7/#9 beat it on miles and CPO.</t>
-        </is>
-      </c>
-      <c r="K4" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cargurus.com/Cars/listing/454596751</t>
-        </is>
-      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>Screened and parked (10)</t>
+        </is>
+      </c>
+      <c r="C4" s="28" t="n"/>
+      <c r="D4" s="28" t="n"/>
+      <c r="E4" s="28" t="n"/>
+      <c r="F4" s="28" t="n"/>
+      <c r="G4" s="28" t="n"/>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="28" t="n"/>
+      <c r="J4" s="28" t="n"/>
+      <c r="K4" s="28" t="n"/>
+      <c r="L4" s="28" t="n"/>
+      <c r="M4" s="28" t="n"/>
+      <c r="N4" s="28" t="n"/>
+      <c r="O4" s="28" t="n"/>
+      <c r="P4" s="28" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Mazda CPO 2022 2.5 S Select, 48,468 mi, $24,081+$299</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>West Hills Mazda, Bremerton</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>WA</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>24081</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>24081</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Cheapest Mazda-CPO car found, but Select trim (comfort-low) + 48k mi; budget backup only.</t>
-        </is>
-      </c>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>https://www.autotrader.com/cars-for-sale/vehicle/786226153</t>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>MY2021–2023 cars that passed the filters but lose to a numbered board car on miles, trim, history or location; re-priced on every sweep in case one moves.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>2023 2.5 S Carbon Edition, 28,928 mi, $27,060+$200</t>
+          <t>Screened and parked</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Titus-Will Used Cars - Olympia</t>
+          <t>2022 2.5 S Carbon Edition, 47,333 mi, $26,998+$200</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>Doug's Lynnwood Mazda</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
           <t>WA</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
-        <v>27260</v>
-      </c>
       <c r="F6" s="9" t="n">
-        <v>27260</v>
-      </c>
-      <c r="G6" s="16" t="n">
+        <v>27198</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>27198</v>
+      </c>
+      <c r="H6" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>$1.6k of drops already; loses to #9 (CPO, same money).</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cargurus.com/Cars/listing/453420840</t>
+      <c r="I6" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K6" s="29" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Fair Deal rating, 47k mi; #7/#9 beat it on miles and CPO.</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cargurus.com/Cars/listing/454596751</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2023 2.5 S Carbon Edition, 23K mi, $28,998</t>
+          <t>Screened and parked</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Rodland Toyota of Everett</t>
+          <t>Mazda CPO 2022 2.5 S Select, 48,468 mi, $24,081+$299</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
+          <t>West Hills Mazda, Bremerton</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
           <t>WA</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>28998</v>
-      </c>
       <c r="F7" s="9" t="n">
-        <v>28998</v>
-      </c>
-      <c r="G7" s="16" t="n">
+        <v>24081</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>24081</v>
+      </c>
+      <c r="H7" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>At the cap before fees; #14 at the same store is the better comfort buy.</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>https://www.autotrader.com/cars-for-sale/vehicle/787184706</t>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="7" t="n"/>
+      <c r="K7" s="29" t="n"/>
+      <c r="L7" s="16" t="n"/>
+      <c r="M7" s="16" t="n"/>
+      <c r="N7" s="3" t="n"/>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>Cheapest Mazda-CPO car found, but Select trim (comfort-low) + 48k mi; budget backup only.</t>
+        </is>
+      </c>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>https://www.autotrader.com/cars-for-sale/vehicle/786226153</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Preferred AWD (year unverified), 33,261 mi, $25,695+$200</t>
+          <t>Screened and parked</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>GoldBoyz Auto Sales, Puyallup (indie)</t>
+          <t>2023 2.5 S Carbon Edition, 28,928 mi, $27,060+$200</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>Titus-Will Used Cars - Olympia</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
           <t>WA</t>
         </is>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>25895</v>
-      </c>
       <c r="F8" s="9" t="n">
-        <v>25895</v>
-      </c>
-      <c r="G8" s="16" t="n">
+        <v>27260</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>27260</v>
+      </c>
+      <c r="H8" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="6" t="n">
-        <v>71</v>
-      </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>Sponsored indie tile, 70 days on market; verify year + history before considering.</t>
-        </is>
-      </c>
-      <c r="K8" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cargurus.com/Cars/listing/449710675</t>
+      <c r="K8" s="29" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="3" t="n"/>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>$1.6k of drops already; loses to #9 (CPO, same money).</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cargurus.com/Cars/listing/453420840</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2022 2.5 S Select, 28,548 mi, $24,995+$200</t>
+          <t>Screened and parked</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Pacific Coast Auto Center, Burlington (indie)</t>
+          <t>2023 2.5 S Carbon Edition, 23K mi, $28,998</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
+          <t>Rodland Toyota of Everett</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
           <t>WA</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>25195</v>
-      </c>
       <c r="F9" s="9" t="n">
-        <v>25195</v>
-      </c>
-      <c r="G9" s="16" t="n">
+        <v>28998</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>28998</v>
+      </c>
+      <c r="H9" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="6" t="n">
-        <v>77</v>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>Fair Deal, Select trim, 75 days; budget tier only.</t>
-        </is>
-      </c>
-      <c r="K9" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cargurus.com/Cars/listing/449233426</t>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="29" t="n"/>
+      <c r="L9" s="16" t="n"/>
+      <c r="M9" s="16" t="n"/>
+      <c r="N9" s="3" t="n"/>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>At the cap before fees; #14 at the same store is the better comfort buy.</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.autotrader.com/cars-for-sale/vehicle/787184706</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2021 Touring, 21,391 mi, $27,999-$28,199</t>
+          <t>Screened and parked</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Mazda of Everett</t>
+          <t>2.5 S Preferred AWD (year unverified), 33,261 mi, $25,695+$200</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>GoldBoyz Auto Sales, Puyallup (indie)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
           <t>WA</t>
         </is>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>27999</v>
-      </c>
       <c r="F10" s="9" t="n">
-        <v>27999</v>
-      </c>
-      <c r="G10" s="16" t="n">
+        <v>25895</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>25895</v>
+      </c>
+      <c r="H10" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Touring = below the comfort bar at a GT price.</t>
-        </is>
-      </c>
-      <c r="K10" s="7" t="inlineStr">
-        <is>
-          <t>https://www.autotrader.com/cars-for-sale/vehicle/787834756</t>
+      <c r="I10" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="K10" s="29" t="n"/>
+      <c r="L10" s="16" t="n"/>
+      <c r="M10" s="16" t="n"/>
+      <c r="N10" s="3" t="n"/>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Sponsored indie tile, 70 days on market; verify year + history before considering.</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cargurus.com/Cars/listing/449710675</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2021 Carbon Edition Turbo, 39,412 mi, $27,722</t>
+          <t>Screened and parked</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Tonkin Gresham Honda</t>
+          <t>2022 2.5 S Select, 28,548 mi, $24,995+$200</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>OR</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>27722</v>
+          <t>Pacific Coast Auto Center, Burlington (indie)</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
       </c>
       <c r="F11" s="9" t="n">
-        <v>27722</v>
-      </c>
-      <c r="G11" s="16" t="n">
+        <v>25195</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>25195</v>
+      </c>
+      <c r="H11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>#4 is the same formula $1.6k cheaper.</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cars.com/vehicledetail/c5fca301-f2de-4480-801a-bed903370d40/</t>
+      <c r="I11" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+      <c r="K11" s="29" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="3" t="n"/>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>Fair Deal, Select trim, 75 days; budget tier only.</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cargurus.com/Cars/listing/449233426</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2023 2.5 S Carbon Edition, 32,594 mi, $27,400</t>
+          <t>Screened and parked</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Lexus of Portland</t>
+          <t>2021 Touring, 21,391 mi, $27,999-$28,199</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>OR</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="n"/>
+          <t>Mazda of Everett</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
       <c r="F12" s="9" t="n">
-        <v>27400</v>
-      </c>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>OR, loses to #9 (WA + CPO) at the same money.</t>
-        </is>
-      </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>https://www.cars.com/vehicledetail/094ebb74-c5d0-4fa6-91f5-9b677cc9e444/</t>
+        <v>27999</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>27999</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="29" t="n"/>
+      <c r="L12" s="16" t="n"/>
+      <c r="M12" s="16" t="n"/>
+      <c r="N12" s="3" t="n"/>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>Touring = below the comfort bar at a GT price.</t>
+        </is>
+      </c>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>https://www.autotrader.com/cars-for-sale/vehicle/787834756</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="7" t="inlineStr">
         <is>
+          <t>Screened and parked</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>2021 Carbon Edition Turbo, 39,412 mi, $27,722</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Tonkin Gresham Honda</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>27722</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>27722</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="29" t="n"/>
+      <c r="L13" s="16" t="n"/>
+      <c r="M13" s="16" t="n"/>
+      <c r="N13" s="3" t="n"/>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>#4 is the same formula $1.6k cheaper.</t>
+        </is>
+      </c>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cars.com/vehicledetail/c5fca301-f2de-4480-801a-bed903370d40/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Screened and parked</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>2023 2.5 S Carbon Edition, 32,594 mi, $27,400</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>Lexus of Portland</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n">
+        <v>27400</v>
+      </c>
+      <c r="H14" s="16" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="29" t="n"/>
+      <c r="L14" s="16" t="n"/>
+      <c r="M14" s="16" t="n"/>
+      <c r="N14" s="3" t="n"/>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>OR, loses to #9 (WA + CPO) at the same money.</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cars.com/vehicledetail/094ebb74-c5d0-4fa6-91f5-9b677cc9e444/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Screened and parked</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
           <t>2023 2.5 S Select, 13,555 mi, $25,950</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Lexus of Portland</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="F15" s="9" t="n">
         <v>25950</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="G15" s="9" t="n">
         <v>25950</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="H15" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="29" t="n"/>
+      <c r="L15" s="16" t="n"/>
+      <c r="M15" s="16" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="inlineStr">
         <is>
           <t>Lowest-mile car found, but Select trim + OR.</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
+      <c r="P15" s="7" t="inlineStr">
         <is>
           <t>https://www.cars.com/vehicledetail/59d3b36d-7131-439c-a3b7-7b91343a454d/</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>2024 model year: watch only (checked Aug 12) (3)</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="28" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="28" t="n"/>
+      <c r="L17" s="28" t="n"/>
+      <c r="M17" s="28" t="n"/>
+      <c r="N17" s="28" t="n"/>
+      <c r="O17" s="28" t="n"/>
+      <c r="P17" s="28" t="n"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>A separate Aug 12 read-only sweep of used 2024 CX-5s (263 VINs; 40 at WA/OR dealers) found no verified-clean, non-rental Preferred / Carbon / Premium under 40k mi that lands at or below the finalists’ est. out-the-door range, so 2024s stay off the numbered board. These three are the ones worth watching; est. OTD = price × (1 + dealer-city rate) + $200 doc + $600 licence, monthly at 6.30% / 60 mo. About 11% of 2024s with a disclosed history are ex-rental or fleet, concentrated in Select / Carbon Edition under $26.5k, so any cheap 2024 needs the Carfax owner-type line first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>2024 model year</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>2024 2.5 S Premium, 18,281 mi, $28,779 ($28,979 on CarGurus w/ doc)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Seattle Finest Motors, Lynnwood (indie)</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>28779</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>28779</v>
+      </c>
+      <c r="H19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+      <c r="K19" s="29" t="inlineStr">
+        <is>
+          <t>JM3KFBDM7R0396688</t>
+        </is>
+      </c>
+      <c r="L19" s="16" t="n">
+        <v>32802</v>
+      </c>
+      <c r="M19" s="16" t="n">
+        <v>639</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>1-own / 0 acc / rental: no (CG flags false)</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>Cheapest verified-clean 2024 Premium (1-owner, 0 accidents, CarGurus fleet/rental flags false, 64 photos); est. OTD lands roughly $800 over #14, Rodland’s 2023 Premium with the same miles, and above every finalist. Independent lot and an early build (VIN R039…), so ask for the in-service date before valuing the extra warranty year.</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cargurus.com/Cars/listing/455108730</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>2024 model year</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>2024 2.5 S Carbon Edition, 35,542 mi, $25,814</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Volkswagen of McMinnville, McMinnville</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>OR</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>25814</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>25814</v>
+      </c>
+      <c r="H20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="29" t="inlineStr">
+        <is>
+          <t>JM3KFBCL9R0527404</t>
+        </is>
+      </c>
+      <c r="L20" s="16" t="n">
+        <v>29466</v>
+      </c>
+      <c r="M20" s="16" t="n">
+        <v>574</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>1-own / 0 acc / rental: unknown</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>Clean on KBB (1-owner, no accidents, +$196 vs FPP) and the only sub-$30k-OTD 2024 above Select with under 40k mi in the region, but 1-owner + 35.5k mi + Carbon Edition on a VW lot fits the ex-rental profile: needs the Carfax owner-type line before anything else. Oregon dealer = email only; 11.05% WA use tax at registration.</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kbb.com/cars-for-sale/vehicle/785745356</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>2024 model year</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>2024 2.5 Carbon Turbo (listed as “Carbon Edition”), 18,446 mi, $29,500</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>McCurley Chevrolet, Pasco</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>29500</v>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>29500</v>
+      </c>
+      <c r="H21" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Great</t>
+        </is>
+      </c>
+      <c r="K21" s="29" t="inlineStr">
+        <is>
+          <t>JM3KFBAY0R0350370</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="n">
+        <v>33560</v>
+      </c>
+      <c r="M21" s="16" t="n">
+        <v>654</v>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>1-own / 0 acc / rental: unknown / dealer-certified (not Mazda CPO)</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>VIN decodes as the Carbon Turbo although the listing says Carbon Edition; ~$3.9k under KBB FPP ($33,430), 1-owner / 0 accidents, GM-dealer “certified” (not Mazda CPO), 5 days listed. Stretch outlier: est. OTD $33,560 at the default rate is over the $32k ceiling and the car is ~215 road-miles away.</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.kbb.com/cars-for-sale/vehicle/787560771</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O32"/>
+  <dimension ref="B1:O33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -5274,7 +5651,7 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="D4" s="27" t="n">
+      <c r="D4" s="30" t="n">
         <v>77</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -5294,7 +5671,7 @@
           <t>ok (VDPs only)</t>
         </is>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="30" t="n">
         <v>41</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -5314,7 +5691,7 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="30" t="n">
         <v>72</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -5334,7 +5711,7 @@
           <t>blocked (fallback ok)</t>
         </is>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="30" t="n">
         <v>10</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -5354,7 +5731,7 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="D8" s="27" t="n">
+      <c r="D8" s="30" t="n">
         <v>47</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -5374,7 +5751,7 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="30" t="n">
         <v>20</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -5394,7 +5771,7 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="30" t="n">
         <v>11</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -5414,7 +5791,7 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="D11" s="27" t="n">
+      <c r="D11" s="30" t="n">
         <v>0</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -5434,7 +5811,7 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="30" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -5454,7 +5831,7 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="30" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -5474,7 +5851,7 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="30" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -5494,7 +5871,7 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="D15" s="27" t="n">
+      <c r="D15" s="30" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -5514,7 +5891,7 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="30" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -5540,82 +5917,89 @@
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
+          <t>Aug 12, 2026: 2024 model-year sweep (read-only, watchlist only). AutoTempest results page (Cars.com, AutoByTel, CarGurus, TrueCar, CarSoup, Carvana cards), CarGurus VDP JSON for all 112 CG ids, KBB SRP __NEXT_DATA__ + KBB pricing page (8 trims), CarMax /cars/api/search/run (nationwide, shippable to 98101), Craigslist Seattle + Portland, NHTSA recalls/complaints. Page loads and JSON GETs only; no forms, contact clicks or accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
           <t>Aug 11, 2026: live re-check in the buyer’s own browser + WA-first re-scan. Live page loads in Evan's own Chrome (residential IP): CarGurus VDP rendered text, KBB VDP, Cars.com VDP/SRP, CarMax VDP, Autotrader SRP, dealer own-site VDP/inventory search. Read-only; no forms touched, no logins.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Honest read: the proxy IP is on Akamai / Cloudflare / DataDome / PerimeterX blocklists, so 6 of 13 direct sources are unreachable. But the blocks cost almost nothing: Autotrader = KBB inventory (got it), TrueCar / Cars.com = AutoTempest feed (got it), CarFax listings = mostly CarGurus overlap. Net-new inventory from round 2 is ~22 cars (KBB-only VINs); everything else was already in round 1 under a different badge.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Dedupe: 278 raw → 153 unique VINs (VIN-matched) + 10 no-VIN orphans. 21 no-VIN records soft-matched to existing VINs by (year, ±1k mi, ±$250) and folded in as “also on” tags.</t>
+          <t>Honest read: the proxy IP is on Akamai / Cloudflare / DataDome / PerimeterX blocklists, so 6 of 13 direct sources are unreachable. But the blocks cost almost nothing: Autotrader = KBB inventory (got it), TrueCar / Cars.com = AutoTempest feed (got it), CarFax listings = mostly CarGurus overlap. Net-new inventory from round 2 is ~22 cars (KBB-only VINs); everything else was already in round 1 under a different badge.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Disqualify: any reported accident, fleet / rental prior use, lemon or frame-damage flag, fewer than 6 photos (where photo count is known), missing VIN (unless Craigslist / iSeeCars-flagged), missing price or miles.</t>
+          <t>Dedupe: 278 raw → 153 unique VINs (VIN-matched) + 10 no-VIN orphans. 21 no-VIN records soft-matched to existing VINs by (year, ±1k mi, ±$250) and folded in as “also on” tags.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Trim: unwanted trims (Sport, Select, base 2.5 S) dropped unless priced more than $3k under the year average.</t>
+          <t>Disqualify: any reported accident, fleet / rental prior use, lemon or frame-damage flag, fewer than 6 photos (where photo count is known), missing VIN (unless Craigslist / iSeeCars-flagged), missing price or miles.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Rank: deal rating / KBB FPP delta → $ below market → 1-owner → CPO → miles per dollar; at least 3 non-CarGurus sources and all 3 model years enforced on the shortlist.</t>
+          <t>Trim: unwanted trims (Sport, Select, base 2.5 S) dropped unless priced more than $3k under the year average.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>NHTSA recalls: 0 open campaigns for MY2021–2023 CX-5 (checked 8/7/26). Verify by VIN at nhtsa.gov/recalls before purchase.</t>
+          <t>Rank: deal rating / KBB FPP delta → $ below market → 1-owner → CPO → miles per dollar; at least 3 non-CarGurus sources and all 3 model years enforced on the shortlist.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Merge: 278 raw records (R1 200 + R2 78) → 153 unique VINs by exact VIN match; 21 no-VIN records soft-matched by (year, ±1k mi, ±$250); 10 no-VIN orphans retained (Craigslist / iSeeCars). Per-source primary contribution after dedupe: CarMax 68, CarGurus 41, KBB 22, Carvana 10, Cars.com 7, iSeeCars 5 orphan, Craigslist 5 orphan, TrueCar 2, CarSoup 2, AutoByTel 1.</t>
+          <t>NHTSA recalls: 0 open campaigns for MY2021–2023 CX-5 (checked 8/7/26). Verify by VIN at nhtsa.gov/recalls before purchase.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>KBB national FPP is default-zip (75201) at “typical” mileage — reads ~$3–5k below Seattle retail across the board. Use the Seattle-derived FPP column for delta math.</t>
+          <t>Merge: 278 raw records (R1 200 + R2 78) → 153 unique VINs by exact VIN match; 21 no-VIN records soft-matched by (year, ±1k mi, ±$250); 10 no-VIN orphans retained (Craigslist / iSeeCars). Per-source primary contribution after dedupe: CarMax 68, CarGurus 41, KBB 22, Carvana 10, Cars.com 7, iSeeCars 5 orphan, Craigslist 5 orphan, TrueCar 2, CarSoup 2, AutoByTel 1.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>#6 KBB record has null kbbFpp (delta shows as −$25,198 in raw data — artifact, ignored).</t>
+          <t>KBB national FPP is default-zip (75201) at “typical” mileage — reads ~$3–5k below Seattle retail across the board. Use the Seattle-derived FPP column for delta math.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>CarMax pick #11: priorUse=[] (no fleet flag); CarMax history report available on the vehicle page.</t>
+          <t>#6 KBB record has null kbbFpp (delta shows as −$25,198 in raw data — artifact, ignored).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>CarMax pick #11: priorUse=[] (no fleet flag); CarMax history report available on the vehicle page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>iSeeCars adds no VINs and no history data — useful only as a cross-listing signal. Craigslist yielded zero private-party sellers in this range.</t>
         </is>

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O20"/>
+  <dimension ref="B1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -604,61 +604,68 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
+          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
+          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
+          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
+          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
+          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
+          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
+          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Aug 7, 2026: Initial read-only market scan: 278 raw listings → 153 unique VINs → 112 pass the disqualifiers; 11-car shortlist ranked by value.</t>
         </is>
@@ -1347,7 +1354,7 @@
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>two-car OTD request (#7 + #12) emailed Aug 11, 3:50 PM; no reply yet.</t>
+          <t>two-car OTD request emailed Aug 11 — both emails to the dealer's listed sales address bounced back Aug 12 (server unreachable after 24h of retries) — the request never arrived; a new contact path is being arranged.</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1741,7 +1748,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>in the Lee Johnson two-car OTD request emailed Aug 11, 3:50 PM; no reply yet.</t>
+          <t>in the Lee Johnson two-car OTD request (Aug 11) — both emails to the dealer's listed sales address bounced back Aug 12 (server unreachable after 24h of retries) — the request never arrived; a new contact path is being arranged.</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O21"/>
+  <dimension ref="B1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>16 cars in play (15 live + benchmark), 5 sold since publication, 5 written quotes in hand.</t>
+          <t>16 cars in play (15 live + benchmark), 5 sold since publication, 7 written quotes in hand.</t>
         </is>
       </c>
     </row>
@@ -604,68 +604,75 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
+          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
+          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
+          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
+          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
+          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
+          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
+          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
+          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Aug 7, 2026: Initial read-only market scan: 278 raw listings → 153 unique VINs → 112 pass the disqualifiers; 11-car shortlist ranked by value.</t>
         </is>
@@ -948,7 +955,7 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>awaiting written OTD; form lead Aug 11 plus a phone promise, nothing received.</t>
+          <t>written itemized quote in hand (sheet dated Aug 11, surfaced Aug 12 after a phone call; the sender's group domain had gone to spam); zero add-ons.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1252,7 +1259,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>awaiting written OTD; same Puyallup lead as #1 (Aug 11), phone promise only.</t>
+          <t>written itemized quote in hand (sheet dated Aug 11, surfaced Aug 12); zero add-ons.</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -1857,7 +1857,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>revised written quote received Aug 11, 4:43 PM with the KARR add-on struck; discussion ongoing.</t>
+          <t>dealer asking to schedule a Saturday time (Aug 12 evening); paperwork requested first.</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -1959,7 +1959,7 @@
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>written quote received Aug 11 (clean sheet; tax and licence lumped in one line, itemization requested); discussion ongoing.</t>
+          <t>dealer declined to negotiate by email (Aug 12 evening); no visit planned.</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O22"/>
+  <dimension ref="B1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Published Aug 7, 2026; refreshed Aug 12, 2026. Generated from data/board.json by tools/build_site.py — same rows as the web page.</t>
+          <t>Published Aug 7, 2026; refreshed Aug 13, 2026. Generated from data/board.json by tools/build_site.py — same rows as the web page.</t>
         </is>
       </c>
     </row>
@@ -604,75 +604,82 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
+          <t>Aug 13, 2026: Hyundai of Kirkland: updated written proposal received midday; license-at-actuals refund and two keys confirmed in writing; window sticker check in progress.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
+          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
+          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
+          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
+          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
+          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
+          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
+          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
+          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Aug 7, 2026: Initial read-only market scan: 278 raw listings → 153 unique VINs → 112 pass the disqualifiers; 11-car shortlist ranked by value.</t>
         </is>
@@ -723,7 +730,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Board — cars in play as of Aug 12, 2026 (sold cars on their own tab)</t>
+          <t>Board — cars in play as of Aug 13, 2026 (sold cars on their own tab)</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
@@ -1159,7 +1166,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>written itemized quote received Aug 11, 4:21 PM (zero add-ons, doc fee at the state cap); reply prepared. KBB lists the dealer as “Ford of Kirkland”; same lot.</t>
+          <t>updated written proposal received Thu Aug 13 midday; license billed at actuals with any overage refunded and two keys confirmed in writing; window sticker being pulled to confirm the GT Premium package.</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -4140,7 +4147,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Watchlist: screened, not on the board (re-checked Aug 12, 2026)</t>
+          <t>Watchlist: screened, not on the board (re-checked Aug 13, 2026)</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
@@ -5001,7 +5008,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>KBB fair purchase price vs. lowest clean live listing (Aug 12, 2026)</t>
+          <t>KBB fair purchase price vs. lowest clean live listing (Aug 13, 2026)</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O23"/>
+  <dimension ref="B1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -604,82 +604,96 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Hyundai of Kirkland: updated written proposal received midday; license-at-actuals refund and two keys confirmed in writing; window sticker check in progress.</t>
+          <t>Aug 13, 2026: Puyallup Mazda: pricing breakdown received for the CPO 2023 Carbon (#9); worksheet attached in email.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
+          <t>Aug 13, 2026: Royal Moore: manager follow-up received Thu afternoon; reply prepared.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
+          <t>Aug 13, 2026: Hyundai of Kirkland: updated written proposal received midday; license-at-actuals refund and two keys confirmed in writing; window sticker check in progress.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
+          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
+          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
+          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
+          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
+          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
+          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
+          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Aug 7, 2026: Initial read-only market scan: 278 raw listings → 153 unique VINs → 112 pass the disqualifiers; 11-car shortlist ranked by value.</t>
         </is>
@@ -1470,7 +1484,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>written quote received Aug 11 as a PDF; it lists Courtesy Guard + Forever Start add-ons and their removal has been requested. Oregon: email-only.</t>
+          <t>a sales manager followed up Thu afternoon; reply prepared.</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -1572,7 +1586,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>folded into the Puyallup #1/#6 inquiry; no written numbers yet.</t>
+          <t>CPO pricing breakdown received Thu Aug 13 early afternoon; itemized worksheet attached in the dealer's email.</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -1180,7 +1180,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>updated written proposal received Thu Aug 13 midday; license billed at actuals with any overage refunded and two keys confirmed in writing; window sticker being pulled to confirm the GT Premium package.</t>
+          <t>updated written proposal received Thu Aug 13 midday; license billed at actuals with any overage refunded and two keys confirmed in writing; window sticker being pulled to confirm the GT Premium package; replied Thu afternoon.</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>a sales manager followed up Thu afternoon; reply prepared.</t>
+          <t>a sales manager followed up Thu afternoon; replied Thu afternoon.</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O25"/>
+  <dimension ref="B1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>16 cars in play (15 live + benchmark), 5 sold since publication, 7 written quotes in hand.</t>
+          <t>15 cars in play (14 live + benchmark), 6 sold since publication, 6 written quotes in hand.</t>
         </is>
       </c>
     </row>
@@ -604,96 +604,103 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Puyallup Mazda: pricing breakdown received for the CPO 2023 Carbon (#9); worksheet attached in email.</t>
+          <t>Aug 13, 2026: Royal Moore: one 2023 Preferred sold per the dealer; the remaining one was requoted with the dealer-added items removed.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Royal Moore: manager follow-up received Thu afternoon; reply prepared.</t>
+          <t>Aug 13, 2026: Puyallup Mazda: pricing breakdown received for the CPO 2023 Carbon (#9); worksheet attached in email.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Hyundai of Kirkland: updated written proposal received midday; license-at-actuals refund and two keys confirmed in writing; window sticker check in progress.</t>
+          <t>Aug 13, 2026: Royal Moore: manager follow-up received Thu afternoon; reply prepared.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
+          <t>Aug 13, 2026: Hyundai of Kirkland: updated written proposal received midday; license-at-actuals refund and two keys confirmed in writing; window sticker check in progress.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
+          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
+          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
+          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
+          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
+          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
+          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
+          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
+          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Aug 7, 2026: Initial read-only market scan: 278 raw listings → 153 unique VINs → 112 pass the disqualifiers; 11-car shortlist ranked by value.</t>
         </is>
@@ -711,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:Y19"/>
+  <dimension ref="B1:Y18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -1393,7 +1400,7 @@
     </row>
     <row r="9">
       <c r="B9" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -1405,7 +1412,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Preferred</t>
+          <t>2.5 S Carbon Edition</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1414,37 +1421,37 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>16615</v>
+        <v>33006</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>26900</v>
+        <v>27699</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>26900</v>
+        <v>27499</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Royal Moore Mazda</t>
+          <t>Puyallup Mazda</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>Hillsboro, OR</t>
+          <t>Puyallup, WA</t>
         </is>
       </c>
       <c r="M9" s="10" t="n">
-        <v>0.1105</v>
+        <v>0.108</v>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Good · $469 below</t>
+          <t>Good · $518 below</t>
         </is>
       </c>
       <c r="O9" s="9" t="n">
-        <v>27590</v>
+        <v>28090</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -1453,11 +1460,11 @@
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R9" s="6" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
@@ -1466,36 +1473,36 @@
       </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/454567468</t>
+          <t>https://www.cargurus.com/Cars/listing/450917825</t>
         </is>
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBCM6P0274841</t>
+          <t>JM3KFBCMXP0288130</t>
         </is>
       </c>
       <c r="V9" s="7" t="inlineStr">
         <is>
-          <t>661788A</t>
+          <t>M260362A</t>
         </is>
       </c>
       <c r="W9" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>a sales manager followed up Thu afternoon; replied Thu afternoon.</t>
+          <t>CPO pricing breakdown received Thu Aug 13 early afternoon; itemized worksheet attached in the dealer's email.</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>Leatherette, heated fronts, power driver seat, moonroof.</t>
+          <t>Red leather, heated fronts, Mazda CPO warranty.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
@@ -1507,7 +1514,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Carbon Edition</t>
+          <t>2.5 S Preferred</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1516,88 +1523,86 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>33006</v>
+        <v>44989</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>27699</v>
+        <v>24095</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>27499</v>
+        <v>23995</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Puyallup Mazda</t>
+          <t>Columbia Sales &amp; Service</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>Puyallup, WA</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="M10" s="10" t="n">
-        <v>0.108</v>
+        <v>0.1105</v>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Good · $518 below</t>
-        </is>
-      </c>
-      <c r="O10" s="9" t="n">
-        <v>28090</v>
-      </c>
+          <t>Great · Cars.com rating</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="n"/>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>1 owner · 0 accidents</t>
+          <t>2 owners · 0 accidents</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R10" s="6" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>CarGurus</t>
+          <t>Cars.com</t>
         </is>
       </c>
       <c r="T10" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/450917825</t>
+          <t>https://www.cars.com/vehicledetail/d4fd9d01-99f9-4673-87c0-1a173ef9551f/</t>
         </is>
       </c>
       <c r="U10" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBCMXP0288130</t>
+          <t>JM3KFBCM9P0119426</t>
         </is>
       </c>
       <c r="V10" s="7" t="inlineStr">
         <is>
-          <t>M260362A</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="W10" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>CPO pricing breakdown received Thu Aug 13 early afternoon; itemized worksheet attached in the dealer's email.</t>
+          <t>emailed Aug 11, no reply. Oregon: email-only.</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>Red leather, heated fronts, Mazda CPO warranty.</t>
+          <t>Leatherette, heated fronts, moonroof.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -1609,7 +1614,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Preferred</t>
+          <t>2.5 S Preferred · Mazda CPO</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1618,49 +1623,43 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>44989</v>
+        <v>36400</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>24095</v>
+        <v>26348</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>23995</v>
+        <v>26348</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Columbia Sales &amp; Service</t>
+          <t>Lee Johnson Mazda of Seattle</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="M11" s="10" t="n">
         <v>0.1105</v>
       </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>Great · Cars.com rating</t>
-        </is>
-      </c>
+      <c r="N11" s="7" t="inlineStr"/>
       <c r="O11" s="9" t="n"/>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>2 owners · 0 accidents</t>
+          <t>0 accidents</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v>29</v>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="n"/>
       <c r="S11" s="7" t="inlineStr">
         <is>
           <t>Cars.com</t>
@@ -1668,36 +1667,32 @@
       </c>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>https://www.cars.com/vehicledetail/d4fd9d01-99f9-4673-87c0-1a173ef9551f/</t>
+          <t>https://www.cars.com/vehicledetail/d7b0a899-fdc8-4776-9379-64684c757f41/</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBCM9P0119426</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="inlineStr">
-        <is>
-          <t>2468</t>
-        </is>
-      </c>
+          <t>JM3KFBCM7P0256994</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="n"/>
       <c r="W11" s="6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>emailed Aug 11, no reply. Oregon: email-only.</t>
+          <t>in the Lee Johnson two-car OTD request (Aug 11) — both emails to the dealer's listed sales address bounced back Aug 12 (server unreachable after 24h of retries) — the request never arrived; a new contact path is being arranged.</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>Leatherette, heated fronts, moonroof.</t>
+          <t>Leather-trimmed Preferred content (heated fronts, moonroof) with the Mazda CPO warranty.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -1705,11 +1700,11 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Preferred · Mazda CPO</t>
+          <t>2.5 S Premium Plus</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1718,76 +1713,88 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>36400</v>
+        <v>43640</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>26348</v>
+        <v>27389</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>26348</v>
+        <v>27389</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>200</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>Lee Johnson Mazda of Seattle</t>
+          <t>Titus-Will Chevrolet GMC Cadillac</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Olympia, WA</t>
         </is>
       </c>
       <c r="M12" s="10" t="n">
-        <v>0.1105</v>
-      </c>
-      <c r="N12" s="7" t="inlineStr"/>
-      <c r="O12" s="9" t="n"/>
+        <v>0.102</v>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>Good · $389 over FPP</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="n">
+        <v>27000</v>
+      </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>0 accidents</t>
+          <t>1 owner · 0 accidents</t>
         </is>
       </c>
       <c r="Q12" s="7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="n"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>45</v>
+      </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>Cars.com</t>
+          <t>KBB</t>
         </is>
       </c>
       <c r="T12" s="7" t="inlineStr">
         <is>
-          <t>https://www.cars.com/vehicledetail/d7b0a899-fdc8-4776-9379-64684c757f41/</t>
+          <t>https://www.kbb.com/cars-for-sale/vehicle/784195725</t>
         </is>
       </c>
       <c r="U12" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBCM7P0256994</t>
-        </is>
-      </c>
-      <c r="V12" s="7" t="n"/>
+          <t>JM3KFBEM1N0590576</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>P11101</t>
+        </is>
+      </c>
       <c r="W12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>in the Lee Johnson two-car OTD request (Aug 11) — both emails to the dealer's listed sales address bounced back Aug 12 (server unreachable after 24h of retries) — the request never arrived; a new contact path is being arranged.</t>
+          <t>dealer asking to schedule a Saturday time (Aug 12 evening); paperwork requested first.</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>Leather-trimmed Preferred content (heated fronts, moonroof) with the Mazda CPO warranty.</t>
+          <t>Ventilated seats, HUD, heated rears; CarBravo (GM) certified, not Mazda CPO.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -1795,11 +1802,11 @@
         </is>
       </c>
       <c r="D13" s="8" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Premium Plus</t>
+          <t>2.5 S Premium</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1808,37 +1815,37 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>43640</v>
+        <v>17505</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>27389</v>
+        <v>28487</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>27389</v>
+        <v>28287</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>200</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Titus-Will Chevrolet GMC Cadillac</t>
+          <t>Rodland Toyota of Everett</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>Olympia, WA</t>
+          <t>Everett, WA</t>
         </is>
       </c>
       <c r="M13" s="10" t="n">
-        <v>0.102</v>
+        <v>0.104</v>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>Good · $389 over FPP</t>
+          <t>Good · $873 below</t>
         </is>
       </c>
       <c r="O13" s="9" t="n">
-        <v>27000</v>
+        <v>27750</v>
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
@@ -1851,49 +1858,49 @@
         </is>
       </c>
       <c r="R13" s="6" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>KBB</t>
+          <t>CarGurus</t>
         </is>
       </c>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>https://www.kbb.com/cars-for-sale/vehicle/784195725</t>
+          <t>https://www.cargurus.com/Cars/listing/453332129</t>
         </is>
       </c>
       <c r="U13" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBEM1N0590576</t>
+          <t>JM3KFBDM7P0281828</t>
         </is>
       </c>
       <c r="V13" s="7" t="inlineStr">
         <is>
-          <t>P11101</t>
+          <t>68987A</t>
         </is>
       </c>
       <c r="W13" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>dealer asking to schedule a Saturday time (Aug 12 evening); paperwork requested first.</t>
+          <t>dealer declined to negotiate by email (Aug 12 evening); no visit planned.</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>Ventilated seats, HUD, heated rears; CarBravo (GM) certified, not Mazda CPO.</t>
+          <t>Lowest-mile comfort car in the set: Soul Red, leather, Bose, heated wheel (no ventilation).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>benchmark</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
@@ -1901,7 +1908,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Premium</t>
+          <t>2.5 S Premium · no-haggle</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1910,38 +1917,36 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>17505</v>
+        <v>31166</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>28487</v>
+        <v>27998</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>28287</v>
+        <v>27998</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>200</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>Rodland Toyota of Everett</t>
+          <t>CarMax Renton</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>Everett, WA</t>
+          <t>Renton, WA</t>
         </is>
       </c>
       <c r="M14" s="10" t="n">
-        <v>0.104</v>
+        <v>0.11</v>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Good · $873 below</t>
-        </is>
-      </c>
-      <c r="O14" s="9" t="n">
-        <v>27750</v>
-      </c>
+          <t>Fair · $222 below</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="n"/>
       <c r="P14" s="7" t="inlineStr">
         <is>
           <t>1 owner · 0 accidents</t>
@@ -1953,57 +1958,57 @@
         </is>
       </c>
       <c r="R14" s="6" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>CarGurus</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="T14" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/453332129</t>
+          <t>https://www.cargurus.com/Cars/listing/455754266</t>
         </is>
       </c>
       <c r="U14" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBDM7P0281828</t>
+          <t>JM3KFBDM0P0215315</t>
         </is>
       </c>
       <c r="V14" s="7" t="inlineStr">
         <is>
-          <t>68987A</t>
+          <t>70134808</t>
         </is>
       </c>
       <c r="W14" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>dealer declined to negotiate by email (Aug 12 evening); no visit planned.</t>
+          <t>reference car; nothing to request.</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>Lowest-mile comfort car in the set: Soul Red, leather, Bose, heated wheel (no ventilation).</t>
+          <t>In-state no-haggle benchmark, no transfer fee.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>benchmark</t>
+          <t>live</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Premium · no-haggle</t>
+          <t>Grand Touring w/ GT Premium pkg</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -2012,39 +2017,41 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>31166</v>
+        <v>30066</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>27998</v>
+        <v>25799</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>27998</v>
+        <v>25799</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>CarMax Renton</t>
+          <t>Auto 206 (independent)</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>Renton, WA</t>
+          <t>Kent, WA</t>
         </is>
       </c>
       <c r="M15" s="10" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Fair · $222 below</t>
-        </is>
-      </c>
-      <c r="O15" s="9" t="n"/>
+          <t>$3,281 &lt; FPP</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="n">
+        <v>29080</v>
+      </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>1 owner · 0 accidents</t>
+          <t>1 owner · 1 accident</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -2053,45 +2060,43 @@
         </is>
       </c>
       <c r="R15" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Autotrader</t>
         </is>
       </c>
       <c r="T15" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/455754266</t>
+          <t>https://www.autotrader.com/cars-for-sale/vehicle/787629893</t>
         </is>
       </c>
       <c r="U15" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBDM0P0215315</t>
+          <t>JM3KFBDM0M0305902</t>
         </is>
       </c>
       <c r="V15" s="7" t="inlineStr">
         <is>
-          <t>70134808</t>
-        </is>
-      </c>
-      <c r="W15" s="6" t="n">
-        <v>6</v>
-      </c>
+          <t>13014</t>
+        </is>
+      </c>
+      <c r="W15" s="6" t="n"/>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>reference car; nothing to request.</t>
+          <t>written offer in hand, valid to Aug 12, 7 PM; Carfax shows a 6/2024 accident. Discussion paused.</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>In-state no-haggle benchmark, no transfer fee.</t>
+          <t>Ventilated seats at GT money (GT Premium package), Deep Crystal Blue.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -2103,50 +2108,50 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Grand Touring w/ GT Premium pkg</t>
+          <t>Signature (2.5T, ventilated)</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.5 Turbo</t>
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>30066</v>
+        <v>40451</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>25799</v>
+        <v>26712</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>25799</v>
+        <v>26712</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Auto 206 (independent)</t>
+          <t>Tonkin Gresham Honda</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>Kent, WA</t>
+          <t>Troutdale, OR</t>
         </is>
       </c>
       <c r="M16" s="10" t="n">
-        <v>0.109</v>
+        <v>0.1105</v>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>$3,281 &lt; FPP</t>
+          <t>Good · $700 below</t>
         </is>
       </c>
       <c r="O16" s="9" t="n">
-        <v>29080</v>
+        <v>24480</v>
       </c>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>1 owner · 1 accident</t>
+          <t>2 owners · 0 accidents</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
@@ -2155,43 +2160,43 @@
         </is>
       </c>
       <c r="R16" s="6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>Autotrader</t>
+          <t>Cars.com</t>
         </is>
       </c>
       <c r="T16" s="7" t="inlineStr">
         <is>
-          <t>https://www.autotrader.com/cars-for-sale/vehicle/787629893</t>
+          <t>https://www.cars.com/vehicledetail/671f18d1-7917-4929-b9c7-3f175ba4013f/</t>
         </is>
       </c>
       <c r="U16" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBDM0M0305902</t>
+          <t>JM3KFBEY2M0349546</t>
         </is>
       </c>
       <c r="V16" s="7" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>G6186020B</t>
         </is>
       </c>
       <c r="W16" s="6" t="n"/>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>written offer in hand, valid to Aug 12, 7 PM; Carfax shows a 6/2024 accident. Discussion paused.</t>
+          <t>not contacted; Oregon fallback, email-only.</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>Ventilated seats at GT money (GT Premium package), Deep Crystal Blue.</t>
+          <t>Top 2021 trim (Nappa, vents, 360 camera).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -2199,54 +2204,48 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Signature (2.5T, ventilated)</t>
+          <t>2.5 S Preferred</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>2.5 Turbo</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>40451</v>
+        <v>16969</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>26712</v>
+        <v>26500</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>26712</v>
+        <v>26500</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>250</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Tonkin Gresham Honda</t>
+          <t>Royal Moore Mazda</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>Troutdale, OR</t>
+          <t>Hillsboro, OR</t>
         </is>
       </c>
       <c r="M17" s="10" t="n">
         <v>0.1105</v>
       </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>Good · $700 below</t>
-        </is>
-      </c>
-      <c r="O17" s="9" t="n">
-        <v>24480</v>
-      </c>
+      <c r="N17" s="7" t="inlineStr"/>
+      <c r="O17" s="9" t="n"/>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>2 owners · 0 accidents</t>
+          <t>0 accidents</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -2264,34 +2263,26 @@
       </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>https://www.cars.com/vehicledetail/671f18d1-7917-4929-b9c7-3f175ba4013f/</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>JM3KFBEY2M0349546</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="inlineStr">
-        <is>
-          <t>G6186020B</t>
-        </is>
-      </c>
+          <t>https://www.cars.com/vehicledetail/84b6552a-4a94-4c5b-96bf-0b3b37cc55a9/</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="n"/>
+      <c r="V17" s="7" t="n"/>
       <c r="W17" s="6" t="n"/>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>not contacted; Oregon fallback, email-only.</t>
+          <t>dealer requoted their remaining 2023 Preferred (stock p12315) Thu Aug 13 with the dealer-added items removed.</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>Top 2021 trim (Nappa, vents, 360 camera).</t>
+          <t>The Royal Moore group's second low-mile Preferred (Toyota store, same auto center as #8).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -2299,48 +2290,54 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Preferred</t>
+          <t>Signature (2.5T)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.5 Turbo</t>
         </is>
       </c>
       <c r="G18" s="6" t="n">
-        <v>16969</v>
+        <v>35589</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>26500</v>
+        <v>25999</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>26500</v>
+        <v>25999</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>Royal Moore Mazda</t>
+          <t>Cortes Auto Center (independent)</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Hillsboro, OR</t>
+          <t>Burlington, WA</t>
         </is>
       </c>
       <c r="M18" s="10" t="n">
-        <v>0.1105</v>
-      </c>
-      <c r="N18" s="7" t="inlineStr"/>
-      <c r="O18" s="9" t="n"/>
+        <v>0.091</v>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>Good · $789 over FPP</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="n">
+        <v>25410</v>
+      </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>0 accidents</t>
+          <t>1 owner · 0 accidents</t>
         </is>
       </c>
       <c r="Q18" s="7" t="inlineStr">
@@ -2349,127 +2346,35 @@
         </is>
       </c>
       <c r="R18" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>Cars.com</t>
+          <t>KBB</t>
         </is>
       </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>https://www.cars.com/vehicledetail/84b6552a-4a94-4c5b-96bf-0b3b37cc55a9/</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="n"/>
-      <c r="V18" s="7" t="n"/>
+          <t>https://www.kbb.com/cars-for-sale/vehicle/787933636</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>JM3KFBEY0M0417715</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>B1851</t>
+        </is>
+      </c>
       <c r="W18" s="6" t="n"/>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>folded into the #8 thread; no separate quote yet. Oregon: email-only.</t>
+          <t>not contacted (found Aug 12).</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>The Royal Moore group's second low-mile Preferred (Toyota store, same auto center as #8).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>2021</v>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>Signature (2.5T)</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>2.5 Turbo</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>35589</v>
-      </c>
-      <c r="H19" s="9" t="n">
-        <v>25999</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>25999</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>Cortes Auto Center (independent)</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>Burlington, WA</t>
-        </is>
-      </c>
-      <c r="M19" s="10" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>Good · $789 over FPP</t>
-        </is>
-      </c>
-      <c r="O19" s="9" t="n">
-        <v>25410</v>
-      </c>
-      <c r="P19" s="7" t="inlineStr">
-        <is>
-          <t>1 owner · 0 accidents</t>
-        </is>
-      </c>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>KBB</t>
-        </is>
-      </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kbb.com/cars-for-sale/vehicle/787933636</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>JM3KFBEY0M0417715</t>
-        </is>
-      </c>
-      <c r="V19" s="7" t="inlineStr">
-        <is>
-          <t>B1851</t>
-        </is>
-      </c>
-      <c r="W19" s="6" t="n"/>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t>not contacted (found Aug 12).</t>
-        </is>
-      </c>
-      <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>WA car, top 2021 trim (Nappa leather, ventilated fronts, 360 camera, turbo), Snowflake White / Caturra Brown.</t>
         </is>
@@ -2642,7 +2547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O31"/>
+  <dimension ref="B1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -3250,16 +3155,16 @@
     </row>
     <row r="17">
       <c r="B17" s="6" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>2023 2.5 S Preferred</t>
+          <t>2021 Signature (2.5T, ventilated)</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Royal Moore Mazda</t>
+          <t>Tonkin Gresham Honda</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
@@ -3268,13 +3173,13 @@
         </is>
       </c>
       <c r="F17" s="9" t="n">
-        <v>26900</v>
+        <v>26712</v>
       </c>
       <c r="G17" s="10" t="n">
         <v>0.1105</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="I17" s="16">
         <f>F17*(1+G17)+H17+$C$6</f>
@@ -3299,22 +3204,22 @@
       </c>
       <c r="O17" s="7" t="inlineStr">
         <is>
-          <t>est. at Hillsboro, OR rate</t>
+          <t>est. at Troutdale, OR rate</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>2021 Signature (2.5T, ventilated)</t>
+          <t>2022 2.5 S Premium Plus</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Tonkin Gresham Honda</t>
+          <t>Titus-Will Chevrolet GMC Cadillac</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -3323,13 +3228,13 @@
         </is>
       </c>
       <c r="F18" s="9" t="n">
-        <v>26712</v>
+        <v>27389</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>0.1105</v>
+        <v>0.102</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="I18" s="16">
         <f>F18*(1+G18)+H18+$C$6</f>
@@ -3354,22 +3259,22 @@
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>est. at Troutdale, OR rate</t>
+          <t>est. at Olympia, WA rate</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>2022 2.5 S Premium Plus</t>
+          <t>2023 2.5 S Carbon Edition</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Titus-Will Chevrolet GMC Cadillac</t>
+          <t>Puyallup Mazda</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -3378,10 +3283,10 @@
         </is>
       </c>
       <c r="F19" s="9" t="n">
-        <v>27389</v>
+        <v>27499</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>0.102</v>
+        <v>0.108</v>
       </c>
       <c r="H19" s="9" t="n">
         <v>200</v>
@@ -3409,22 +3314,22 @@
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>est. at Olympia, WA rate</t>
+          <t>est. at Puyallup, WA rate</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>2023 2.5 S Carbon Edition</t>
+          <t>2022 2.5 S Carbon Edition</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Puyallup Mazda</t>
+          <t>Lee Johnson Mazda of Seattle</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -3433,10 +3338,10 @@
         </is>
       </c>
       <c r="F20" s="9" t="n">
-        <v>27499</v>
+        <v>27512</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>0.108</v>
+        <v>0.1105</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>200</v>
@@ -3464,22 +3369,22 @@
       </c>
       <c r="O20" s="7" t="inlineStr">
         <is>
-          <t>est. at Puyallup, WA rate</t>
+          <t>est. at Seattle, WA rate</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>2022 2.5 S Carbon Edition</t>
+          <t>2023 2.5 Turbo AWD</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Lee Johnson Mazda of Seattle</t>
+          <t>Puyallup Mazda</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -3488,10 +3393,10 @@
         </is>
       </c>
       <c r="F21" s="9" t="n">
-        <v>27512</v>
+        <v>27999</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>0.1105</v>
+        <v>0.108</v>
       </c>
       <c r="H21" s="9" t="n">
         <v>200</v>
@@ -3519,192 +3424,174 @@
       </c>
       <c r="O21" s="7" t="inlineStr">
         <is>
-          <t>est. at Seattle, WA rate</t>
+          <t>est. at Puyallup, WA rate</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>2023 2.5 Turbo AWD</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>Puyallup Mazda</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="B22" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>2023 2.5 S Premium · no-haggle (benchmark)</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>CarMax Renton</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
-      <c r="F22" s="9" t="n">
-        <v>27999</v>
-      </c>
-      <c r="G22" s="10" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="H22" s="9" t="n">
+      <c r="F22" s="20" t="n">
+        <v>27998</v>
+      </c>
+      <c r="G22" s="21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H22" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="22">
         <f>F22*(1+G22)+H22+$C$6</f>
         <v/>
       </c>
-      <c r="J22" s="17" t="n"/>
-      <c r="K22" s="12">
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="24">
         <f>IF(J22&gt;0,J22,I22)</f>
         <v/>
       </c>
-      <c r="L22" s="16">
+      <c r="L22" s="22">
         <f>-PMT($C$3/12,$C$4,K22)</f>
         <v/>
       </c>
-      <c r="M22" s="16">
+      <c r="M22" s="22">
         <f>-PMT($C$3/12,$C$4,MAX(0,K22-$C$5))</f>
         <v/>
       </c>
-      <c r="N22" s="16">
+      <c r="N22" s="22">
         <f>L22*$C$4-K22</f>
         <v/>
       </c>
-      <c r="O22" s="7" t="inlineStr">
-        <is>
-          <t>est. at Puyallup, WA rate</t>
+      <c r="O22" s="19" t="inlineStr">
+        <is>
+          <t>est. at Renton, WA rate</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>2023 2.5 S Premium · no-haggle (benchmark)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>CarMax Renton</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="B23" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>2023 2.5 S Premium</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Rodland Toyota of Everett</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
-      <c r="F23" s="20" t="n">
-        <v>27998</v>
-      </c>
-      <c r="G23" s="21" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H23" s="20" t="n">
+      <c r="F23" s="9" t="n">
+        <v>28287</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="H23" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="16">
         <f>F23*(1+G23)+H23+$C$6</f>
         <v/>
       </c>
-      <c r="J23" s="23" t="n"/>
-      <c r="K23" s="24">
+      <c r="J23" s="17" t="n"/>
+      <c r="K23" s="12">
         <f>IF(J23&gt;0,J23,I23)</f>
         <v/>
       </c>
-      <c r="L23" s="22">
+      <c r="L23" s="16">
         <f>-PMT($C$3/12,$C$4,K23)</f>
         <v/>
       </c>
-      <c r="M23" s="22">
+      <c r="M23" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K23-$C$5))</f>
         <v/>
       </c>
-      <c r="N23" s="22">
+      <c r="N23" s="16">
         <f>L23*$C$4-K23</f>
         <v/>
       </c>
-      <c r="O23" s="19" t="inlineStr">
-        <is>
-          <t>est. at Renton, WA rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>2023 2.5 S Premium</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>Rodland Toyota of Everett</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="O23" s="7" t="inlineStr">
+        <is>
+          <t>est. at Everett, WA rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Cheapest solid vs. stretch</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Cheapest solid</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>#5 2021 Grand Touring AWD · Hyundai of Kirkland</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
-      <c r="F24" s="9" t="n">
-        <v>28287</v>
-      </c>
-      <c r="G24" s="10" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="H24" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I24" s="16">
-        <f>F24*(1+G24)+H24+$C$6</f>
-        <v/>
-      </c>
-      <c r="J24" s="17" t="n"/>
-      <c r="K24" s="12">
-        <f>IF(J24&gt;0,J24,I24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="16">
-        <f>-PMT($C$3/12,$C$4,K24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="16">
-        <f>-PMT($C$3/12,$C$4,MAX(0,K24-$C$5))</f>
-        <v/>
-      </c>
-      <c r="N24" s="16">
-        <f>L24*$C$4-K24</f>
-        <v/>
-      </c>
-      <c r="O24" s="7" t="inlineStr">
-        <is>
-          <t>est. at Everett, WA rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Cheapest solid vs. stretch</t>
-        </is>
+      <c r="F26" s="16" t="n">
+        <v>25192</v>
+      </c>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
+      <c r="K26" s="16" t="n">
+        <v>28712.736</v>
+      </c>
+      <c r="L26" s="16" t="n">
+        <v>559.1117635962995</v>
+      </c>
+      <c r="M26" s="16" t="n">
+        <v>461.7487391188865</v>
+      </c>
+      <c r="N26" s="16" t="n">
+        <v>4833.969815777968</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="7" t="n"/>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Cheapest solid</t>
+          <t>Stretch</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>#5 2021 Grand Touring AWD · Hyundai of Kirkland</t>
+          <t>#1 2023 2.5 Turbo AWD · Puyallup Mazda</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -3713,93 +3600,56 @@
         </is>
       </c>
       <c r="F27" s="16" t="n">
-        <v>25192</v>
+        <v>27999</v>
       </c>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="16" t="n">
-        <v>28712.736</v>
+        <v>31822.892</v>
       </c>
       <c r="L27" s="16" t="n">
-        <v>559.1117635962995</v>
+        <v>619.6746025476141</v>
       </c>
       <c r="M27" s="16" t="n">
-        <v>461.7487391188865</v>
+        <v>522.3115780702011</v>
       </c>
       <c r="N27" s="16" t="n">
-        <v>4833.969815777968</v>
+        <v>5357.584152856845</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>#1 2023 2.5 Turbo AWD · Puyallup Mazda</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
-      <c r="F28" s="16" t="n">
-        <v>27999</v>
-      </c>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="16" t="n">
-        <v>31822.892</v>
-      </c>
-      <c r="L28" s="16" t="n">
-        <v>619.6746025476141</v>
-      </c>
-      <c r="M28" s="16" t="n">
-        <v>522.3115780702011</v>
-      </c>
-      <c r="N28" s="16" t="n">
-        <v>5357.584152856845</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="25" t="n"/>
-      <c r="C29" s="25" t="inlineStr">
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="25" t="inlineStr">
         <is>
           <t>Δ</t>
         </is>
       </c>
-      <c r="D29" s="25" t="n"/>
-      <c r="E29" s="25" t="n"/>
-      <c r="F29" s="26" t="n">
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="26" t="n">
         <v>2807</v>
       </c>
-      <c r="G29" s="25" t="n"/>
-      <c r="H29" s="25" t="n"/>
-      <c r="I29" s="25" t="n"/>
-      <c r="J29" s="25" t="n"/>
-      <c r="K29" s="26" t="n">
+      <c r="G28" s="25" t="n"/>
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="25" t="n"/>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="26" t="n">
         <v>3110.156000000003</v>
       </c>
-      <c r="L29" s="26" t="n">
+      <c r="L28" s="26" t="n">
         <v>60.56283895131457</v>
       </c>
-      <c r="M29" s="26" t="n">
+      <c r="M28" s="26" t="n">
         <v>60.56283895131463</v>
       </c>
-      <c r="N29" s="26" t="n">
+      <c r="N28" s="26" t="n">
         <v>523.6143370788777</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="14" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>Rule: cheapest solid = lowest estimated out-the-door figure among live cars with a verified 1-owner / 0-accident history (or Mazda CPO) at a franchise dealer; stretch = best-value live 2023 in the Turbo / Premium tiers, ranked by list price against KBB Seattle fair purchase price.</t>
         </is>
@@ -3817,7 +3667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O8"/>
+  <dimension ref="B1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -3995,75 +3845,75 @@
     </row>
     <row r="6">
       <c r="B6" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Carbon Edition</t>
+          <t>2.5 S Preferred AWD</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>CarMax Sacramento South</t>
+          <t>Royal Moore Mazda</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Hillsboro, OR</t>
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>24998</v>
+        <v>26900</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>48337</v>
+        <v>16615</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Aug 11</t>
+          <t>Aug 13</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Aug 11 PM</t>
+          <t>dealer email Aug 13</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>https://www.carmax.com/car/70056694</t>
+          <t>https://www.cargurus.com/Cars/listing/454567468</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Grand Touring AWD</t>
+          <t>Carbon Edition</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Doug's Lynnwood Mazda</t>
+          <t>CarMax Sacramento South</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Edmonds, WA</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="G7" s="9" t="n">
-        <v>28700</v>
+        <v>24998</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>27089</v>
+        <v>48337</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -4072,54 +3922,98 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>dealer email Aug 11 (sold Aug 10)</t>
+          <t>Aug 11 PM</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.cars.com/vehicledetail/495a1e58-37a7-480b-9f80-8bb411d8fa8f/</t>
+          <t>https://www.carmax.com/car/70056694</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Grand Touring AWD</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Doug's Lynnwood Mazda</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Edmonds, WA</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>28700</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>27089</v>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Aug 11</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>dealer email Aug 11 (sold Aug 10)</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cars.com/vehicledetail/495a1e58-37a7-480b-9f80-8bb411d8fa8f/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="C8" s="8" t="n">
+      <c r="C9" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>2.5 S Preferred AWD</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>Auto Connections of Bellevue (independent)</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G9" s="9" t="n">
         <v>26495</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H9" s="6" t="n">
         <v>20533</v>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>Aug 11</t>
         </is>
       </c>
-      <c r="J8" s="7" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Aug 11, 11:51 AM</t>
         </is>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr">
         <is>
           <t>https://www.cargurus.com/Cars/listing/450670232</t>
         </is>
@@ -5466,7 +5360,7 @@
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O26"/>
+  <dimension ref="B1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -548,7 +548,7 @@
     <row r="3">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Published Aug 7, 2026; refreshed Aug 13, 2026. Generated from data/board.json by tools/build_site.py — same rows as the web page.</t>
+          <t>Published Aug 7, 2026; refreshed Aug 14, 2026. Generated from data/board.json by tools/build_site.py — same rows as the web page.</t>
         </is>
       </c>
     </row>
@@ -604,103 +604,110 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Royal Moore: one 2023 Preferred sold per the dealer; the remaining one was requoted with the dealer-added items removed.</t>
+          <t>Aug 14, 2026: Titus-Will: dealer confirmed their best number and stood down; the Olympia car is off the weekend visit list.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Puyallup Mazda: pricing breakdown received for the CPO 2023 Carbon (#9); worksheet attached in email.</t>
+          <t>Aug 13, 2026: Royal Moore: one 2023 Preferred sold per the dealer; the remaining one was requoted with the dealer-added items removed.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Royal Moore: manager follow-up received Thu afternoon; reply prepared.</t>
+          <t>Aug 13, 2026: Puyallup Mazda: pricing breakdown received for the CPO 2023 Carbon (#9); worksheet attached in email.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Hyundai of Kirkland: updated written proposal received midday; license-at-actuals refund and two keys confirmed in writing; window sticker check in progress.</t>
+          <t>Aug 13, 2026: Royal Moore: manager follow-up received Thu afternoon; reply prepared.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
+          <t>Aug 13, 2026: Hyundai of Kirkland: updated written proposal received midday; license-at-actuals refund and two keys confirmed in writing; window sticker check in progress.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
+          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
+          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
+          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
+          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
+          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
+          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
+          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
+          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Aug 7, 2026: Initial read-only market scan: 278 raw listings → 153 unique VINs → 112 pass the disqualifiers; 11-car shortlist ranked by value.</t>
         </is>
@@ -751,7 +758,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Board — cars in play as of Aug 13, 2026 (sold cars on their own tab)</t>
+          <t>Board — cars in play as of Aug 14, 2026 (sold cars on their own tab)</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
@@ -1783,7 +1790,7 @@
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>dealer asking to schedule a Saturday time (Aug 12 evening); paperwork requested first.</t>
+          <t>dealer confirmed their best number Fri Aug 14 and left the door open; not on this weekend's visit list.</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -4055,7 +4062,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Watchlist: screened, not on the board (re-checked Aug 13, 2026)</t>
+          <t>Watchlist: screened, not on the board (re-checked Aug 14, 2026)</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>
@@ -4916,7 +4923,7 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>KBB fair purchase price vs. lowest clean live listing (Aug 13, 2026)</t>
+          <t>KBB fair purchase price vs. lowest clean live listing (Aug 14, 2026)</t>
         </is>
       </c>
       <c r="C1" s="2" t="n"/>

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O27"/>
+  <dimension ref="B1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>15 cars in play (14 live + benchmark), 6 sold since publication, 6 written quotes in hand.</t>
+          <t>15 cars in play (14 live + benchmark), 6 sold since publication, 7 written quotes in hand.</t>
         </is>
       </c>
     </row>
@@ -604,110 +604,117 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Aug 14, 2026: Titus-Will: dealer confirmed their best number and stood down; the Olympia car is off the weekend visit list.</t>
+          <t>Aug 14, 2026: Puyallup Mazda: itemized worksheet received for the certified 2023 Carbon (#9); zero add-ons.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Royal Moore: one 2023 Preferred sold per the dealer; the remaining one was requoted with the dealer-added items removed.</t>
+          <t>Aug 14, 2026: Titus-Will: dealer confirmed their best number and stood down; the Olympia car is off the weekend visit list.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Puyallup Mazda: pricing breakdown received for the CPO 2023 Carbon (#9); worksheet attached in email.</t>
+          <t>Aug 13, 2026: Royal Moore: one 2023 Preferred sold per the dealer; the remaining one was requoted with the dealer-added items removed.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Royal Moore: manager follow-up received Thu afternoon; reply prepared.</t>
+          <t>Aug 13, 2026: Puyallup Mazda: pricing breakdown received for the CPO 2023 Carbon (#9); worksheet attached in email.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Hyundai of Kirkland: updated written proposal received midday; license-at-actuals refund and two keys confirmed in writing; window sticker check in progress.</t>
+          <t>Aug 13, 2026: Royal Moore: manager follow-up received Thu afternoon; reply prepared.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
+          <t>Aug 13, 2026: Hyundai of Kirkland: updated written proposal received midday; license-at-actuals refund and two keys confirmed in writing; window sticker check in progress.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
+          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
+          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
+          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
+          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
+          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
+          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
+          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
+          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Aug 7, 2026: Initial read-only market scan: 278 raw listings → 153 unique VINs → 112 pass the disqualifiers; 11-car shortlist ranked by value.</t>
         </is>
@@ -1498,7 +1505,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>CPO pricing breakdown received Thu Aug 13 early afternoon; itemized worksheet attached in the dealer's email.</t>
+          <t>itemized written worksheet received Fri Aug 14; zero add-ons and the selling price came in under the advertised figure.</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -1165,7 +1165,7 @@
       </c>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>1 owner · 0 accidents</t>
+          <t>1 owner · 1 accident</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>updated written proposal received Thu Aug 13 midday; license billed at actuals with any overage refunded and two keys confirmed in writing; window sticker being pulled to confirm the GT Premium package; replied Thu afternoon.</t>
+          <t>CARFAX read in full Sat Aug 15: one owner, Washington only, 12 dealer service records and no open recalls, but an accident reported 7/31/2021 with no severity, no impact location and no repair record. Previously carried here as accident-free, which was wrong.</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>#5 2021 Grand Touring AWD · Hyundai of Kirkland</t>
+          <t>#4 2021 Carbon Edition Turbo · Ron Tonkin Honda</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -3577,23 +3577,23 @@
         </is>
       </c>
       <c r="F26" s="16" t="n">
-        <v>25192</v>
+        <v>25852</v>
       </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="16" t="n">
-        <v>28712.736</v>
+        <v>29558.646</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>559.1117635962995</v>
+        <v>575.5838348034372</v>
       </c>
       <c r="M26" s="16" t="n">
-        <v>461.7487391188865</v>
+        <v>478.2208103260242</v>
       </c>
       <c r="N26" s="16" t="n">
-        <v>4833.969815777968</v>
+        <v>4976.384088206229</v>
       </c>
     </row>
     <row r="27">
@@ -3643,23 +3643,23 @@
       <c r="D28" s="25" t="n"/>
       <c r="E28" s="25" t="n"/>
       <c r="F28" s="26" t="n">
-        <v>2807</v>
+        <v>2147</v>
       </c>
       <c r="G28" s="25" t="n"/>
       <c r="H28" s="25" t="n"/>
       <c r="I28" s="25" t="n"/>
       <c r="J28" s="25" t="n"/>
       <c r="K28" s="26" t="n">
-        <v>3110.156000000003</v>
+        <v>2264.246000000003</v>
       </c>
       <c r="L28" s="26" t="n">
-        <v>60.56283895131457</v>
+        <v>44.0907677441769</v>
       </c>
       <c r="M28" s="26" t="n">
-        <v>60.56283895131463</v>
+        <v>44.09076774417696</v>
       </c>
       <c r="N28" s="26" t="n">
-        <v>523.6143370788777</v>
+        <v>381.2000646506167</v>
       </c>
     </row>
     <row r="30">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="I5" s="7" t="inlineStr"/>
       <c r="J5" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -1201,12 +1201,12 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>CARFAX read in full Sat Aug 15: one owner, Washington only, 12 dealer service records and no open recalls, but an accident reported 7/31/2021 with no severity, no impact location and no repair record. Previously carried here as accident-free, which was wrong.</t>
+          <t>Seen in person Sat Aug 15. The GT Premium package is confirmed on the dealer window sheet. The car did not start during the visit, the dealer suspects the battery and took it into their shop, so no test drive happened. Price discussion continuing by phone.</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>Leather, Bose, moonroof; GT Premium pkg adds ventilated fronts, heated rears + wheel, HUD.</t>
+          <t>Confirmed on the window sheet: ventilated front seats, heated rear seats, heated steering wheel, Active Driving Display, power folding mirrors, wiper de-icer. Leather, Bose, moonroof. Rear camera only.</t>
         </is>
       </c>
     </row>

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -930,10 +930,10 @@
         <v>27990</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>28199</v>
+        <v>27919</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>27999</v>
+        <v>27719</v>
       </c>
       <c r="J4" s="9" t="n">
         <v>200</v>
@@ -997,12 +997,12 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>written itemized quote in hand (sheet dated Aug 11, surfaced Aug 12 after a phone call; the sender's group domain had gone to spam); zero add-ons.</t>
+          <t>Seen and driven Sat Aug 15. The original window sticker confirms the full comfort package including ventilated front seats, and the CARFAX shows one owner, a personal lease and no accidents.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Loaded turbo: heated leather, Bose, sunroof, 227 hp.</t>
+          <t>Confirmed on the original window sticker: ventilated front seats, heated front and rear seats, heated steering wheel, Active Driving Display, wireless charger, power folding mirrors, Bose 10-speaker, driver seat memory, moonroof. 2.5 Turbo, 227 hp on 87 octane and 256 hp on 93.</t>
         </is>
       </c>
     </row>
@@ -1236,10 +1236,10 @@
         <v>42515</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>25198</v>
+        <v>24948</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>24998</v>
+        <v>24748</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>200</v>
@@ -1265,7 +1265,7 @@
       <c r="O7" s="9" t="n"/>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>2 owners · 0 accidents</t>
+          <t>3 owners · 0 accidents</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>written itemized quote in hand (sheet dated Aug 11, surfaced Aug 12); zero add-ons.</t>
+          <t>CARFAX read in full Sat Aug 15. A Canadian-market car with a Saskatchewan safety-inspection failure recorded 8/15/2025 and no repair record after it, imported to the United States in May 2026 and sold at auction in June. Removed from consideration.</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1438,10 +1438,10 @@
         <v>33006</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>27699</v>
+        <v>27424</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>27499</v>
+        <v>27224</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>200</v>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>itemized written worksheet received Fri Aug 14; zero add-ons and the selling price came in under the advertised figure.</t>
+          <t>Seen Sat Aug 15. The dealer CARFAX link for this vehicle would not load, so its history remains unverified.</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F10" s="9" t="n">
-        <v>24998</v>
+        <v>24748</v>
       </c>
       <c r="G10" s="10" t="n">
         <v>0.108</v>
@@ -3224,16 +3224,16 @@
     </row>
     <row r="18">
       <c r="B18" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>2022 2.5 S Premium Plus</t>
+          <t>2023 2.5 S Carbon Edition</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Titus-Will Chevrolet GMC Cadillac</t>
+          <t>Puyallup Mazda</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="F18" s="9" t="n">
-        <v>27389</v>
+        <v>27224</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>0.102</v>
+        <v>0.108</v>
       </c>
       <c r="H18" s="9" t="n">
         <v>200</v>
@@ -3273,22 +3273,22 @@
       </c>
       <c r="O18" s="7" t="inlineStr">
         <is>
-          <t>est. at Olympia, WA rate</t>
+          <t>est. at Puyallup, WA rate</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>2023 2.5 S Carbon Edition</t>
+          <t>2022 2.5 S Premium Plus</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Puyallup Mazda</t>
+          <t>Titus-Will Chevrolet GMC Cadillac</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F19" s="9" t="n">
-        <v>27499</v>
+        <v>27389</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>0.108</v>
+        <v>0.102</v>
       </c>
       <c r="H19" s="9" t="n">
         <v>200</v>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="O19" s="7" t="inlineStr">
         <is>
-          <t>est. at Puyallup, WA rate</t>
+          <t>est. at Olympia, WA rate</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="F21" s="9" t="n">
-        <v>27999</v>
+        <v>27719</v>
       </c>
       <c r="G21" s="10" t="n">
         <v>0.108</v>
@@ -3614,23 +3614,23 @@
         </is>
       </c>
       <c r="F27" s="16" t="n">
-        <v>27999</v>
+        <v>27719</v>
       </c>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="7" t="n"/>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n"/>
       <c r="K27" s="16" t="n">
-        <v>31822.892</v>
+        <v>31512.652</v>
       </c>
       <c r="L27" s="16" t="n">
-        <v>619.6746025476141</v>
+        <v>613.6334216048396</v>
       </c>
       <c r="M27" s="16" t="n">
-        <v>522.3115780702011</v>
+        <v>516.2703971274266</v>
       </c>
       <c r="N27" s="16" t="n">
-        <v>5357.584152856845</v>
+        <v>5305.35329629037</v>
       </c>
     </row>
     <row r="28">
@@ -3643,23 +3643,23 @@
       <c r="D28" s="25" t="n"/>
       <c r="E28" s="25" t="n"/>
       <c r="F28" s="26" t="n">
-        <v>2147</v>
+        <v>1867</v>
       </c>
       <c r="G28" s="25" t="n"/>
       <c r="H28" s="25" t="n"/>
       <c r="I28" s="25" t="n"/>
       <c r="J28" s="25" t="n"/>
       <c r="K28" s="26" t="n">
-        <v>2264.246000000003</v>
+        <v>1954.006000000001</v>
       </c>
       <c r="L28" s="26" t="n">
-        <v>44.0907677441769</v>
+        <v>38.04958680140237</v>
       </c>
       <c r="M28" s="26" t="n">
-        <v>44.09076774417696</v>
+        <v>38.04958680140243</v>
       </c>
       <c r="N28" s="26" t="n">
-        <v>381.2000646506167</v>
+        <v>328.9692080841414</v>
       </c>
     </row>
     <row r="30">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n">
-        <v>25198</v>
+        <v>24948</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>30980</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>28199</v>
+        <v>27919</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>

--- a/CX5-Seattle-Buyers-Report.xlsx
+++ b/CX5-Seattle-Buyers-Report.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O28"/>
+  <dimension ref="B1:O32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -555,7 +555,7 @@
     <row r="4">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>15 cars in play (14 live + benchmark), 6 sold since publication, 7 written quotes in hand.</t>
+          <t>14 cars in play (13 live + benchmark), 7 sold since publication, 6 written quotes in hand.</t>
         </is>
       </c>
     </row>
@@ -604,117 +604,145 @@
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Aug 14, 2026: Puyallup Mazda: itemized worksheet received for the certified 2023 Carbon (#9); zero add-ons.</t>
+          <t>Aug 15, 2026: Search closed. The buyer purchased the 2023 CX-5 2.5 Turbo AWD (VIN JM3KFBAY3P0289626, 27,990 miles) from Puyallup Mazda on Aug 15 2026.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Aug 14, 2026: Titus-Will: dealer confirmed their best number and stood down; the Olympia car is off the weekend visit list.</t>
+          <t>Aug 15, 2026: The board is frozen as of that date. Prices, availability and history notes on the remaining cars reflect the last verification before close and are no longer being maintained.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Royal Moore: one 2023 Preferred sold per the dealer; the remaining one was requoted with the dealer-added items removed.</t>
+          <t>Aug 15, 2026: Verified in person that day: the 2023 Turbo's original window sticker (full comfort package standard on the 25T trim) and a clean one-owner CARFAX.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Puyallup Mazda: pricing breakdown received for the CPO 2023 Carbon (#9); worksheet attached in email.</t>
+          <t>Aug 15, 2026: Removed from consideration: Puyallup's red 2021, a Canadian-market car whose CARFAX records a Saskatchewan safety-inspection failure on 8/15/2025 with no repair record after it.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Royal Moore: manager follow-up received Thu afternoon; reply prepared.</t>
+          <t>Aug 14, 2026: Puyallup Mazda: itemized worksheet received for the certified 2023 Carbon (#9); zero add-ons.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Aug 13, 2026: Hyundai of Kirkland: updated written proposal received midday; license-at-actuals refund and two keys confirmed in writing; window sticker check in progress.</t>
+          <t>Aug 14, 2026: Titus-Will: dealer confirmed their best number and stood down; the Olympia car is off the weekend visit list.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
+          <t>Aug 13, 2026: Royal Moore: one 2023 Preferred sold per the dealer; the remaining one was requoted with the dealer-added items removed.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
+          <t>Aug 13, 2026: Puyallup Mazda: pricing breakdown received for the CPO 2023 Carbon (#9); worksheet attached in email.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
+          <t>Aug 13, 2026: Royal Moore: manager follow-up received Thu afternoon; reply prepared.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
+          <t>Aug 13, 2026: Hyundai of Kirkland: updated written proposal received midday; license-at-actuals refund and two keys confirmed in writing; window sticker check in progress.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
+          <t>Aug 12, 2026: Puyallup Mazda (#1, #6): written itemized quotes surfaced (sheets dated Aug 11 had landed in spam); zero add-ons on both. #9's breakdown requested.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
+          <t>Aug 12, 2026: Lee Johnson (#7, #12): both inquiry emails bounced back undelivered (dealer mail server unreachable); a new contact path is being arranged.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
+          <t>Aug 12, 2026: Fresh read-only sweep (AutoTempest, CarGurus, KBB, CarMax, Carvana, Craigslist: 386 raw / 223 VINs). Every live board car re-verified with no listed-price change; #12 (Cars.com-only) could not be re-checked from the sweep environment.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
+          <t>Aug 12, 2026: 26 VINs not seen before: 25 disqualified (unwanted trim, out-of-area no-haggle units no better than #15, no value signal), 1 added as #21 (2021 Signature, Burlington WA, $25,999 + $200).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
+          <t>Aug 12, 2026: Rodland (#14) pricing sheet transcribed: clean sheet, no add-ons; tax and licence lumped in one line, itemization requested.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+          <t>Aug 12, 2026: Site now regenerates every section and download from one board file, so the cost table, compare box, calculator and top picks follow the live set (sold #3 dropped from the picks; quoted OTDs replace estimates where dealers have replied).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Aug 12, 2026: 2024 model-year sweep — no verified-clean, non-rental 2024 Preferred/Carbon/Premium under 40k mi lands at or below the finalists’ $28.7–32k est. OTD; three 2024s added to the watchlist (watch only, not numbered board cars).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Buyer outreach began: itemized-OTD requests to every live dealer; written numbers back from Kirkland (#5), Titus-Will (#13, revised), Auto 206 (#17), Rodland (#14) and Royal Moore (#8, add-ons to strike).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Sold and removed: #2 Acura of Seattle Turbo, #3 BMW Seattle GT Reserve (dealer-confirmed), #11 CarMax Sacramento, #16 Doug’s Lynnwood GT, #18 Auto Connections Bellevue. #1’s reported sale was wrong (live on CarGurus and Puyallup Mazda’s own site at $27,999).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Aug 11, 2026: Comfort-first re-rank and WA-first re-scan added #12–#20; tax model corrected to dealer-city rates (Seattle 11.05%) from the flat 10.35% used on Aug 7.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Aug 7, 2026: Initial read-only market scan: 278 raw listings → 153 unique VINs → 112 pass the disqualifiers; 11-car shortlist ranked by value.</t>
         </is>
@@ -732,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:Y18"/>
+  <dimension ref="B1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -906,7 +934,7 @@
     </row>
     <row r="4">
       <c r="B4" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
@@ -914,11 +942,11 @@
         </is>
       </c>
       <c r="D4" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>2.5 Turbo AWD</t>
+          <t>Carbon Edition Turbo</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -927,37 +955,37 @@
         </is>
       </c>
       <c r="G4" s="6" t="n">
-        <v>27990</v>
+        <v>34800</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>27919</v>
+        <v>26102</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>27719</v>
+        <v>25852</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>Puyallup Mazda</t>
+          <t>Ron Tonkin Honda</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Puyallup, WA</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="M4" s="10" t="n">
-        <v>0.108</v>
+        <v>0.1105</v>
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>Great · $2,781 &lt; FPP</t>
+          <t>Great · $2,612 &lt; FPP</t>
         </is>
       </c>
       <c r="O4" s="9" t="n">
-        <v>30980</v>
+        <v>29374</v>
       </c>
       <c r="P4" s="7" t="inlineStr">
         <is>
@@ -970,45 +998,45 @@
         </is>
       </c>
       <c r="R4" s="6" t="n">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>CarGurus</t>
+          <t>KBB</t>
         </is>
       </c>
       <c r="T4" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/448185375</t>
+          <t>https://www.kbb.com/cars-for-sale/vehicle/782577606</t>
         </is>
       </c>
       <c r="U4" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBAY3P0289626</t>
+          <t>JM3KFBCYXM0385696</t>
         </is>
       </c>
       <c r="V4" s="7" t="inlineStr">
         <is>
-          <t>YW29065</t>
+          <t>UH1679</t>
         </is>
       </c>
       <c r="W4" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>Seen and driven Sat Aug 15. The original window sticker confirms the full comfort package including ventilated front seats, and the CARFAX shows one owner, a personal lease and no accidents.</t>
+          <t>quote in preparation (Aug 11, 3:57 PM); our written-number request is with the dealer. Oregon: email-only leverage.</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>Confirmed on the original window sticker: ventilated front seats, heated front and rear seats, heated steering wheel, Active Driving Display, wireless charger, power folding mirrors, Bose 10-speaker, driver seat memory, moonroof. 2.5 Turbo, 227 hp on 87 octane and 256 hp on 93.</t>
+          <t>Carbon look, heated seats; turbo confirmed by the dealer.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -1020,50 +1048,50 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Carbon Edition Turbo</t>
+          <t>Grand Touring AWD</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>2.5 Turbo</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>34800</v>
+        <v>33336</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>26102</v>
+        <v>25192</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>25852</v>
+        <v>25192</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>Ron Tonkin Honda</t>
+          <t>Hyundai of Kirkland / Ford of Kirkland</t>
         </is>
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Kirkland, WA</t>
         </is>
       </c>
       <c r="M5" s="10" t="n">
-        <v>0.1105</v>
+        <v>0.108</v>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>Great · $2,612 &lt; FPP</t>
+          <t>Good · $3,338 &lt; FPP</t>
         </is>
       </c>
       <c r="O5" s="9" t="n">
-        <v>29374</v>
+        <v>28530</v>
       </c>
       <c r="P5" s="7" t="inlineStr">
         <is>
-          <t>1 owner · 0 accidents</t>
+          <t>1 owner · 1 accident</t>
         </is>
       </c>
       <c r="Q5" s="7" t="inlineStr">
@@ -1072,45 +1100,45 @@
         </is>
       </c>
       <c r="R5" s="6" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>KBB</t>
+          <t>CarGurus</t>
         </is>
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>https://www.kbb.com/cars-for-sale/vehicle/782577606</t>
+          <t>https://www.cargurus.com/Cars/listing/451807182</t>
         </is>
       </c>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBCYXM0385696</t>
+          <t>JM3KFBDM3M0301052</t>
         </is>
       </c>
       <c r="V5" s="7" t="inlineStr">
         <is>
-          <t>UH1679</t>
+          <t>O94564A</t>
         </is>
       </c>
       <c r="W5" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>quote in preparation (Aug 11, 3:57 PM); our written-number request is with the dealer. Oregon: email-only leverage.</t>
+          <t>Seen in person Sat Aug 15. The GT Premium package is confirmed on the dealer window sheet. The car did not start during the visit, the dealer suspects the battery and took it into their shop, so no test drive happened. Price discussion continuing by phone.</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>Carbon look, heated seats; turbo confirmed by the dealer.</t>
+          <t>Confirmed on the window sheet: ventilated front seats, heated rear seats, heated steering wheel, Active Driving Display, power folding mirrors, wiper de-icer. Leather, Bose, moonroof. Rear camera only.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
@@ -1122,34 +1150,34 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Grand Touring AWD</t>
+          <t>Carbon Ed Turbo AWD</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.5 Turbo</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>33336</v>
+        <v>42515</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>25192</v>
+        <v>24948</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>25192</v>
+        <v>24748</v>
       </c>
       <c r="J6" s="9" t="n">
         <v>200</v>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>Hyundai of Kirkland / Ford of Kirkland</t>
+          <t>Puyallup Mazda</t>
         </is>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>Kirkland, WA</t>
+          <t>Puyallup, WA</t>
         </is>
       </c>
       <c r="M6" s="10" t="n">
@@ -1157,15 +1185,13 @@
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>Good · $3,338 &lt; FPP</t>
-        </is>
-      </c>
-      <c r="O6" s="9" t="n">
-        <v>28530</v>
-      </c>
+          <t>Great · $1,939 below</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="n"/>
       <c r="P6" s="7" t="inlineStr">
         <is>
-          <t>1 owner · 1 accident</t>
+          <t>3 owners · 0 accidents</t>
         </is>
       </c>
       <c r="Q6" s="7" t="inlineStr">
@@ -1174,7 +1200,7 @@
         </is>
       </c>
       <c r="R6" s="6" t="n">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
@@ -1183,36 +1209,36 @@
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/451807182</t>
+          <t>https://www.cargurus.com/Cars/listing/449972241</t>
         </is>
       </c>
       <c r="U6" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBDM3M0301052</t>
+          <t>JM3KFBDYXM0120596</t>
         </is>
       </c>
       <c r="V6" s="7" t="inlineStr">
         <is>
-          <t>O94564A</t>
+          <t>YS29241</t>
         </is>
       </c>
       <c r="W6" s="6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>Seen in person Sat Aug 15. The GT Premium package is confirmed on the dealer window sheet. The car did not start during the visit, the dealer suspects the battery and took it into their shop, so no test drive happened. Price discussion continuing by phone.</t>
+          <t>CARFAX read in full Sat Aug 15. A Canadian-market car with a Saskatchewan safety-inspection failure recorded 8/15/2025 and no repair record after it, imported to the United States in May 2026 and sold at auction in June. Removed from consideration.</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>Confirmed on the window sheet: ventilated front seats, heated rear seats, heated steering wheel, Active Driving Display, power folding mirrors, wiper de-icer. Leather, Bose, moonroof. Rear camera only.</t>
+          <t>Carbon look: Soul Red, black 19s, heated seats, turbo.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
@@ -1220,61 +1246,63 @@
         </is>
       </c>
       <c r="D7" s="8" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Carbon Ed Turbo AWD</t>
+          <t>2.5 S Carbon Edition</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>2.5 Turbo</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>42515</v>
+        <v>34749</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>24948</v>
+        <v>27512</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>24748</v>
+        <v>27512</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>200</v>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>Puyallup Mazda</t>
+          <t>Lee Johnson Mazda of Seattle</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>Puyallup, WA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="M7" s="10" t="n">
-        <v>0.108</v>
+        <v>0.1105</v>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>Great · $1,939 below</t>
-        </is>
-      </c>
-      <c r="O7" s="9" t="n"/>
+          <t>Good · $349 below</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="n">
+        <v>27440</v>
+      </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>3 owners · 0 accidents</t>
+          <t>1 owner · 0 accidents</t>
         </is>
       </c>
       <c r="Q7" s="7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="R7" s="6" t="n">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
@@ -1283,36 +1311,36 @@
       </c>
       <c r="T7" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/449972241</t>
+          <t>https://www.cargurus.com/Cars/listing/453287059</t>
         </is>
       </c>
       <c r="U7" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBDYXM0120596</t>
+          <t>JM3KFBCM4N0546820</t>
         </is>
       </c>
       <c r="V7" s="7" t="inlineStr">
         <is>
-          <t>YS29241</t>
+          <t>U14590</t>
         </is>
       </c>
       <c r="W7" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>CARFAX read in full Sat Aug 15. A Canadian-market car with a Saskatchewan safety-inspection failure recorded 8/15/2025 and no repair record after it, imported to the United States in May 2026 and sold at auction in June. Removed from consideration.</t>
+          <t>two-car OTD request emailed Aug 11 — both emails to the dealer's listed sales address bounced back Aug 12 (server unreachable after 24h of retries) — the request never arrived; a new contact path is being arranged.</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>Carbon look: Soul Red, black 19s, heated seats, turbo.</t>
+          <t>Red leather, heated fronts, moonroof, Mazda CPO warranty.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -1320,7 +1348,7 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
@@ -1333,37 +1361,37 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>34749</v>
+        <v>33006</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>27512</v>
+        <v>27424</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>27512</v>
+        <v>27224</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>200</v>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>Lee Johnson Mazda of Seattle</t>
+          <t>Puyallup Mazda</t>
         </is>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Puyallup, WA</t>
         </is>
       </c>
       <c r="M8" s="10" t="n">
-        <v>0.1105</v>
+        <v>0.108</v>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>Good · $349 below</t>
+          <t>Good · $518 below</t>
         </is>
       </c>
       <c r="O8" s="9" t="n">
-        <v>27440</v>
+        <v>28090</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -1376,7 +1404,7 @@
         </is>
       </c>
       <c r="R8" s="6" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
@@ -1385,36 +1413,36 @@
       </c>
       <c r="T8" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/453287059</t>
+          <t>https://www.cargurus.com/Cars/listing/450917825</t>
         </is>
       </c>
       <c r="U8" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBCM4N0546820</t>
+          <t>JM3KFBCMXP0288130</t>
         </is>
       </c>
       <c r="V8" s="7" t="inlineStr">
         <is>
-          <t>U14590</t>
+          <t>M260362A</t>
         </is>
       </c>
       <c r="W8" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>two-car OTD request emailed Aug 11 — both emails to the dealer's listed sales address bounced back Aug 12 (server unreachable after 24h of retries) — the request never arrived; a new contact path is being arranged.</t>
+          <t>Seen Sat Aug 15. The dealer CARFAX link for this vehicle would not load, so its history remains unverified.</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>Red leather, heated fronts, moonroof, Mazda CPO warranty.</t>
+          <t>Red leather, heated fronts, Mazda CPO warranty.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -1426,7 +1454,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Carbon Edition</t>
+          <t>2.5 S Preferred</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1435,88 +1463,86 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>33006</v>
+        <v>44989</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>27424</v>
+        <v>24095</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>27224</v>
+        <v>23995</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>Puyallup Mazda</t>
+          <t>Columbia Sales &amp; Service</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>Puyallup, WA</t>
+          <t>Portland, OR</t>
         </is>
       </c>
       <c r="M9" s="10" t="n">
-        <v>0.108</v>
+        <v>0.1105</v>
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Good · $518 below</t>
-        </is>
-      </c>
-      <c r="O9" s="9" t="n">
-        <v>28090</v>
-      </c>
+          <t>Great · Cars.com rating</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="n"/>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>1 owner · 0 accidents</t>
+          <t>2 owners · 0 accidents</t>
         </is>
       </c>
       <c r="Q9" s="7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R9" s="6" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>CarGurus</t>
+          <t>Cars.com</t>
         </is>
       </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/450917825</t>
+          <t>https://www.cars.com/vehicledetail/d4fd9d01-99f9-4673-87c0-1a173ef9551f/</t>
         </is>
       </c>
       <c r="U9" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBCMXP0288130</t>
+          <t>JM3KFBCM9P0119426</t>
         </is>
       </c>
       <c r="V9" s="7" t="inlineStr">
         <is>
-          <t>M260362A</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="W9" s="6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>Seen Sat Aug 15. The dealer CARFAX link for this vehicle would not load, so its history remains unverified.</t>
+          <t>emailed Aug 11, no reply. Oregon: email-only.</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>Red leather, heated fronts, Mazda CPO warranty.</t>
+          <t>Leatherette, heated fronts, moonroof.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
@@ -1528,7 +1554,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Preferred</t>
+          <t>2.5 S Preferred · Mazda CPO</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1537,49 +1563,43 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>44989</v>
+        <v>36400</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>24095</v>
+        <v>26348</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>23995</v>
+        <v>26348</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>Columbia Sales &amp; Service</t>
+          <t>Lee Johnson Mazda of Seattle</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>Portland, OR</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="M10" s="10" t="n">
         <v>0.1105</v>
       </c>
-      <c r="N10" s="7" t="inlineStr">
-        <is>
-          <t>Great · Cars.com rating</t>
-        </is>
-      </c>
+      <c r="N10" s="7" t="inlineStr"/>
       <c r="O10" s="9" t="n"/>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>2 owners · 0 accidents</t>
+          <t>0 accidents</t>
         </is>
       </c>
       <c r="Q10" s="7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v>29</v>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="n"/>
       <c r="S10" s="7" t="inlineStr">
         <is>
           <t>Cars.com</t>
@@ -1587,36 +1607,32 @@
       </c>
       <c r="T10" s="7" t="inlineStr">
         <is>
-          <t>https://www.cars.com/vehicledetail/d4fd9d01-99f9-4673-87c0-1a173ef9551f/</t>
+          <t>https://www.cars.com/vehicledetail/d7b0a899-fdc8-4776-9379-64684c757f41/</t>
         </is>
       </c>
       <c r="U10" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBCM9P0119426</t>
-        </is>
-      </c>
-      <c r="V10" s="7" t="inlineStr">
-        <is>
-          <t>2468</t>
-        </is>
-      </c>
+          <t>JM3KFBCM7P0256994</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="n"/>
       <c r="W10" s="6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>emailed Aug 11, no reply. Oregon: email-only.</t>
+          <t>in the Lee Johnson two-car OTD request (Aug 11) — both emails to the dealer's listed sales address bounced back Aug 12 (server unreachable after 24h of retries) — the request never arrived; a new contact path is being arranged.</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>Leatherette, heated fronts, moonroof.</t>
+          <t>Leather-trimmed Preferred content (heated fronts, moonroof) with the Mazda CPO warranty.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -1624,11 +1640,11 @@
         </is>
       </c>
       <c r="D11" s="8" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Preferred · Mazda CPO</t>
+          <t>2.5 S Premium Plus</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -1637,76 +1653,88 @@
         </is>
       </c>
       <c r="G11" s="6" t="n">
-        <v>36400</v>
+        <v>43640</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>26348</v>
+        <v>27389</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>26348</v>
+        <v>27389</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>200</v>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>Lee Johnson Mazda of Seattle</t>
+          <t>Titus-Will Chevrolet GMC Cadillac</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Olympia, WA</t>
         </is>
       </c>
       <c r="M11" s="10" t="n">
-        <v>0.1105</v>
-      </c>
-      <c r="N11" s="7" t="inlineStr"/>
-      <c r="O11" s="9" t="n"/>
+        <v>0.102</v>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>Good · $389 over FPP</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="n">
+        <v>27000</v>
+      </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>0 accidents</t>
+          <t>1 owner · 0 accidents</t>
         </is>
       </c>
       <c r="Q11" s="7" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="n"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v>45</v>
+      </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>Cars.com</t>
+          <t>KBB</t>
         </is>
       </c>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>https://www.cars.com/vehicledetail/d7b0a899-fdc8-4776-9379-64684c757f41/</t>
+          <t>https://www.kbb.com/cars-for-sale/vehicle/784195725</t>
         </is>
       </c>
       <c r="U11" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBCM7P0256994</t>
-        </is>
-      </c>
-      <c r="V11" s="7" t="n"/>
+          <t>JM3KFBEM1N0590576</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>P11101</t>
+        </is>
+      </c>
       <c r="W11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>in the Lee Johnson two-car OTD request (Aug 11) — both emails to the dealer's listed sales address bounced back Aug 12 (server unreachable after 24h of retries) — the request never arrived; a new contact path is being arranged.</t>
+          <t>dealer confirmed their best number Fri Aug 14 and left the door open; not on this weekend's visit list.</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>Leather-trimmed Preferred content (heated fronts, moonroof) with the Mazda CPO warranty.</t>
+          <t>Ventilated seats, HUD, heated rears; CarBravo (GM) certified, not Mazda CPO.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -1714,11 +1742,11 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Premium Plus</t>
+          <t>2.5 S Premium</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1727,37 +1755,37 @@
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>43640</v>
+        <v>17505</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>27389</v>
+        <v>28487</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>27389</v>
+        <v>28287</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>200</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>Titus-Will Chevrolet GMC Cadillac</t>
+          <t>Rodland Toyota of Everett</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>Olympia, WA</t>
+          <t>Everett, WA</t>
         </is>
       </c>
       <c r="M12" s="10" t="n">
-        <v>0.102</v>
+        <v>0.104</v>
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>Good · $389 over FPP</t>
+          <t>Good · $873 below</t>
         </is>
       </c>
       <c r="O12" s="9" t="n">
-        <v>27000</v>
+        <v>27750</v>
       </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
@@ -1770,49 +1798,49 @@
         </is>
       </c>
       <c r="R12" s="6" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>KBB</t>
+          <t>CarGurus</t>
         </is>
       </c>
       <c r="T12" s="7" t="inlineStr">
         <is>
-          <t>https://www.kbb.com/cars-for-sale/vehicle/784195725</t>
+          <t>https://www.cargurus.com/Cars/listing/453332129</t>
         </is>
       </c>
       <c r="U12" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBEM1N0590576</t>
+          <t>JM3KFBDM7P0281828</t>
         </is>
       </c>
       <c r="V12" s="7" t="inlineStr">
         <is>
-          <t>P11101</t>
+          <t>68987A</t>
         </is>
       </c>
       <c r="W12" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>dealer confirmed their best number Fri Aug 14 and left the door open; not on this weekend's visit list.</t>
+          <t>dealer declined to negotiate by email (Aug 12 evening); no visit planned.</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>Ventilated seats, HUD, heated rears; CarBravo (GM) certified, not Mazda CPO.</t>
+          <t>Lowest-mile comfort car in the set: Soul Red, leather, Bose, heated wheel (no ventilation).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>live</t>
+          <t>benchmark</t>
         </is>
       </c>
       <c r="D13" s="8" t="n">
@@ -1820,7 +1848,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Premium</t>
+          <t>2.5 S Premium · no-haggle</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1829,38 +1857,36 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>17505</v>
+        <v>31166</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>28487</v>
+        <v>27998</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>28287</v>
+        <v>27998</v>
       </c>
       <c r="J13" s="9" t="n">
         <v>200</v>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Rodland Toyota of Everett</t>
+          <t>CarMax Renton</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>Everett, WA</t>
+          <t>Renton, WA</t>
         </is>
       </c>
       <c r="M13" s="10" t="n">
-        <v>0.104</v>
+        <v>0.11</v>
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>Good · $873 below</t>
-        </is>
-      </c>
-      <c r="O13" s="9" t="n">
-        <v>27750</v>
-      </c>
+          <t>Fair · $222 below</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="n"/>
       <c r="P13" s="7" t="inlineStr">
         <is>
           <t>1 owner · 0 accidents</t>
@@ -1872,57 +1898,57 @@
         </is>
       </c>
       <c r="R13" s="6" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>CarGurus</t>
+          <t>CarMax</t>
         </is>
       </c>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/453332129</t>
+          <t>https://www.cargurus.com/Cars/listing/455754266</t>
         </is>
       </c>
       <c r="U13" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBDM7P0281828</t>
+          <t>JM3KFBDM0P0215315</t>
         </is>
       </c>
       <c r="V13" s="7" t="inlineStr">
         <is>
-          <t>68987A</t>
+          <t>70134808</t>
         </is>
       </c>
       <c r="W13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>dealer declined to negotiate by email (Aug 12 evening); no visit planned.</t>
+          <t>reference car; nothing to request.</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>Lowest-mile comfort car in the set: Soul Red, leather, Bose, heated wheel (no ventilation).</t>
+          <t>In-state no-haggle benchmark, no transfer fee.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>benchmark</t>
+          <t>live</t>
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Premium · no-haggle</t>
+          <t>Grand Touring w/ GT Premium pkg</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1931,39 +1957,41 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>31166</v>
+        <v>30066</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>27998</v>
+        <v>25799</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>27998</v>
+        <v>25799</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>CarMax Renton</t>
+          <t>Auto 206 (independent)</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>Renton, WA</t>
+          <t>Kent, WA</t>
         </is>
       </c>
       <c r="M14" s="10" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Fair · $222 below</t>
-        </is>
-      </c>
-      <c r="O14" s="9" t="n"/>
+          <t>$3,281 &lt; FPP</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>29080</v>
+      </c>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>1 owner · 0 accidents</t>
+          <t>1 owner · 1 accident</t>
         </is>
       </c>
       <c r="Q14" s="7" t="inlineStr">
@@ -1972,45 +2000,43 @@
         </is>
       </c>
       <c r="R14" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>CarMax</t>
+          <t>Autotrader</t>
         </is>
       </c>
       <c r="T14" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/455754266</t>
+          <t>https://www.autotrader.com/cars-for-sale/vehicle/787629893</t>
         </is>
       </c>
       <c r="U14" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBDM0P0215315</t>
+          <t>JM3KFBDM0M0305902</t>
         </is>
       </c>
       <c r="V14" s="7" t="inlineStr">
         <is>
-          <t>70134808</t>
-        </is>
-      </c>
-      <c r="W14" s="6" t="n">
-        <v>6</v>
-      </c>
+          <t>13014</t>
+        </is>
+      </c>
+      <c r="W14" s="6" t="n"/>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>reference car; nothing to request.</t>
+          <t>written offer in hand, valid to Aug 12, 7 PM; Carfax shows a 6/2024 accident. Discussion paused.</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>In-state no-haggle benchmark, no transfer fee.</t>
+          <t>Ventilated seats at GT money (GT Premium package), Deep Crystal Blue.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -2022,50 +2048,50 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Grand Touring w/ GT Premium pkg</t>
+          <t>Signature (2.5T, ventilated)</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.5 Turbo</t>
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>30066</v>
+        <v>40451</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>25799</v>
+        <v>26712</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>25799</v>
+        <v>26712</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>Auto 206 (independent)</t>
+          <t>Tonkin Gresham Honda</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>Kent, WA</t>
+          <t>Troutdale, OR</t>
         </is>
       </c>
       <c r="M15" s="10" t="n">
-        <v>0.109</v>
+        <v>0.1105</v>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>$3,281 &lt; FPP</t>
+          <t>Good · $700 below</t>
         </is>
       </c>
       <c r="O15" s="9" t="n">
-        <v>29080</v>
+        <v>24480</v>
       </c>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>1 owner · 1 accident</t>
+          <t>2 owners · 0 accidents</t>
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr">
@@ -2074,43 +2100,43 @@
         </is>
       </c>
       <c r="R15" s="6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>Autotrader</t>
+          <t>Cars.com</t>
         </is>
       </c>
       <c r="T15" s="7" t="inlineStr">
         <is>
-          <t>https://www.autotrader.com/cars-for-sale/vehicle/787629893</t>
+          <t>https://www.cars.com/vehicledetail/671f18d1-7917-4929-b9c7-3f175ba4013f/</t>
         </is>
       </c>
       <c r="U15" s="7" t="inlineStr">
         <is>
-          <t>JM3KFBDM0M0305902</t>
+          <t>JM3KFBEY2M0349546</t>
         </is>
       </c>
       <c r="V15" s="7" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>G6186020B</t>
         </is>
       </c>
       <c r="W15" s="6" t="n"/>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>written offer in hand, valid to Aug 12, 7 PM; Carfax shows a 6/2024 accident. Discussion paused.</t>
+          <t>not contacted; Oregon fallback, email-only.</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>Ventilated seats at GT money (GT Premium package), Deep Crystal Blue.</t>
+          <t>Top 2021 trim (Nappa, vents, 360 camera).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
@@ -2118,54 +2144,48 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Signature (2.5T, ventilated)</t>
+          <t>2.5 S Preferred</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>2.5 Turbo</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>40451</v>
+        <v>16969</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>26712</v>
+        <v>26500</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>26712</v>
+        <v>26500</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>250</v>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>Tonkin Gresham Honda</t>
+          <t>Royal Moore Mazda</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>Troutdale, OR</t>
+          <t>Hillsboro, OR</t>
         </is>
       </c>
       <c r="M16" s="10" t="n">
         <v>0.1105</v>
       </c>
-      <c r="N16" s="7" t="inlineStr">
-        <is>
-          <t>Good · $700 below</t>
-        </is>
-      </c>
-      <c r="O16" s="9" t="n">
-        <v>24480</v>
-      </c>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="9" t="n"/>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>2 owners · 0 accidents</t>
+          <t>0 accidents</t>
         </is>
       </c>
       <c r="Q16" s="7" t="inlineStr">
@@ -2183,34 +2203,26 @@
       </c>
       <c r="T16" s="7" t="inlineStr">
         <is>
-          <t>https://www.cars.com/vehicledetail/671f18d1-7917-4929-b9c7-3f175ba4013f/</t>
-        </is>
-      </c>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>JM3KFBEY2M0349546</t>
-        </is>
-      </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>G6186020B</t>
-        </is>
-      </c>
+          <t>https://www.cars.com/vehicledetail/84b6552a-4a94-4c5b-96bf-0b3b37cc55a9/</t>
+        </is>
+      </c>
+      <c r="U16" s="7" t="n"/>
+      <c r="V16" s="7" t="n"/>
       <c r="W16" s="6" t="n"/>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>not contacted; Oregon fallback, email-only.</t>
+          <t>dealer requoted their remaining 2023 Preferred (stock p12315) Thu Aug 13 with the dealer-added items removed.</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>Top 2021 trim (Nappa, vents, 360 camera).</t>
+          <t>The Royal Moore group's second low-mile Preferred (Toyota store, same auto center as #8).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -2218,48 +2230,54 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Preferred</t>
+          <t>Signature (2.5T)</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.5 Turbo</t>
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>16969</v>
+        <v>35589</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>26500</v>
+        <v>25999</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>26500</v>
+        <v>25999</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>Royal Moore Mazda</t>
+          <t>Cortes Auto Center (independent)</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>Hillsboro, OR</t>
+          <t>Burlington, WA</t>
         </is>
       </c>
       <c r="M17" s="10" t="n">
-        <v>0.1105</v>
-      </c>
-      <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="9" t="n"/>
+        <v>0.091</v>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>Good · $789 over FPP</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="n">
+        <v>25410</v>
+      </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>0 accidents</t>
+          <t>1 owner · 0 accidents</t>
         </is>
       </c>
       <c r="Q17" s="7" t="inlineStr">
@@ -2268,127 +2286,35 @@
         </is>
       </c>
       <c r="R17" s="6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>Cars.com</t>
+          <t>KBB</t>
         </is>
       </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>https://www.cars.com/vehicledetail/84b6552a-4a94-4c5b-96bf-0b3b37cc55a9/</t>
-        </is>
-      </c>
-      <c r="U17" s="7" t="n"/>
-      <c r="V17" s="7" t="n"/>
+          <t>https://www.kbb.com/cars-for-sale/vehicle/787933636</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>JM3KFBEY0M0417715</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>B1851</t>
+        </is>
+      </c>
       <c r="W17" s="6" t="n"/>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>dealer requoted their remaining 2023 Preferred (stock p12315) Thu Aug 13 with the dealer-added items removed.</t>
+          <t>not contacted (found Aug 12).</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>The Royal Moore group's second low-mile Preferred (Toyota store, same auto center as #8).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>live</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>2021</v>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>Signature (2.5T)</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>2.5 Turbo</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>35589</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>25999</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>25999</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>Cortes Auto Center (independent)</t>
-        </is>
-      </c>
-      <c r="L18" s="7" t="inlineStr">
-        <is>
-          <t>Burlington, WA</t>
-        </is>
-      </c>
-      <c r="M18" s="10" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>Good · $789 over FPP</t>
-        </is>
-      </c>
-      <c r="O18" s="9" t="n">
-        <v>25410</v>
-      </c>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>1 owner · 0 accidents</t>
-        </is>
-      </c>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>KBB</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr">
-        <is>
-          <t>https://www.kbb.com/cars-for-sale/vehicle/787933636</t>
-        </is>
-      </c>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>JM3KFBEY0M0417715</t>
-        </is>
-      </c>
-      <c r="V18" s="7" t="inlineStr">
-        <is>
-          <t>B1851</t>
-        </is>
-      </c>
-      <c r="W18" s="6" t="n"/>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t>not contacted (found Aug 12).</t>
-        </is>
-      </c>
-      <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>WA car, top 2021 trim (Nappa leather, ventilated fronts, 360 camera, turbo), Snowflake White / Caturra Brown.</t>
         </is>
@@ -2561,7 +2487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O30"/>
+  <dimension ref="B1:O29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -3388,187 +3314,169 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>2023 2.5 Turbo AWD</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Puyallup Mazda</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="B21" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>2023 2.5 S Premium · no-haggle (benchmark)</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>CarMax Renton</t>
+        </is>
+      </c>
+      <c r="E21" s="19" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
-      <c r="F21" s="9" t="n">
-        <v>27719</v>
-      </c>
-      <c r="G21" s="10" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="H21" s="9" t="n">
+      <c r="F21" s="20" t="n">
+        <v>27998</v>
+      </c>
+      <c r="G21" s="21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H21" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="22">
         <f>F21*(1+G21)+H21+$C$6</f>
         <v/>
       </c>
-      <c r="J21" s="17" t="n"/>
-      <c r="K21" s="12">
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="24">
         <f>IF(J21&gt;0,J21,I21)</f>
         <v/>
       </c>
-      <c r="L21" s="16">
+      <c r="L21" s="22">
         <f>-PMT($C$3/12,$C$4,K21)</f>
         <v/>
       </c>
-      <c r="M21" s="16">
+      <c r="M21" s="22">
         <f>-PMT($C$3/12,$C$4,MAX(0,K21-$C$5))</f>
         <v/>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="22">
         <f>L21*$C$4-K21</f>
         <v/>
       </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>est. at Puyallup, WA rate</t>
+      <c r="O21" s="19" t="inlineStr">
+        <is>
+          <t>est. at Renton, WA rate</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>2023 2.5 S Premium · no-haggle (benchmark)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>CarMax Renton</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
+      <c r="B22" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>2023 2.5 S Premium</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Rodland Toyota of Everett</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
-      <c r="F22" s="20" t="n">
-        <v>27998</v>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H22" s="20" t="n">
+      <c r="F22" s="9" t="n">
+        <v>28287</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="H22" s="9" t="n">
         <v>200</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="16">
         <f>F22*(1+G22)+H22+$C$6</f>
         <v/>
       </c>
-      <c r="J22" s="23" t="n"/>
-      <c r="K22" s="24">
+      <c r="J22" s="17" t="n"/>
+      <c r="K22" s="12">
         <f>IF(J22&gt;0,J22,I22)</f>
         <v/>
       </c>
-      <c r="L22" s="22">
+      <c r="L22" s="16">
         <f>-PMT($C$3/12,$C$4,K22)</f>
         <v/>
       </c>
-      <c r="M22" s="22">
+      <c r="M22" s="16">
         <f>-PMT($C$3/12,$C$4,MAX(0,K22-$C$5))</f>
         <v/>
       </c>
-      <c r="N22" s="22">
+      <c r="N22" s="16">
         <f>L22*$C$4-K22</f>
         <v/>
       </c>
-      <c r="O22" s="19" t="inlineStr">
-        <is>
-          <t>est. at Renton, WA rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>2023 2.5 S Premium</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Rodland Toyota of Everett</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="O22" s="7" t="inlineStr">
+        <is>
+          <t>est. at Everett, WA rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Cheapest solid vs. stretch</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Cheapest solid</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>#4 2021 Carbon Edition Turbo · Ron Tonkin Honda</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>est</t>
         </is>
       </c>
-      <c r="F23" s="9" t="n">
-        <v>28287</v>
-      </c>
-      <c r="G23" s="10" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="H23" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="I23" s="16">
-        <f>F23*(1+G23)+H23+$C$6</f>
-        <v/>
-      </c>
-      <c r="J23" s="17" t="n"/>
-      <c r="K23" s="12">
-        <f>IF(J23&gt;0,J23,I23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="16">
-        <f>-PMT($C$3/12,$C$4,K23)</f>
-        <v/>
-      </c>
-      <c r="M23" s="16">
-        <f>-PMT($C$3/12,$C$4,MAX(0,K23-$C$5))</f>
-        <v/>
-      </c>
-      <c r="N23" s="16">
-        <f>L23*$C$4-K23</f>
-        <v/>
-      </c>
-      <c r="O23" s="7" t="inlineStr">
-        <is>
-          <t>est. at Everett, WA rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Cheapest solid vs. stretch</t>
-        </is>
+      <c r="F25" s="16" t="n">
+        <v>25852</v>
+      </c>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="16" t="n">
+        <v>29558.646</v>
+      </c>
+      <c r="L25" s="16" t="n">
+        <v>575.5838348034372</v>
+      </c>
+      <c r="M25" s="16" t="n">
+        <v>478.2208103260242</v>
+      </c>
+      <c r="N25" s="16" t="n">
+        <v>4976.384088206229</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="7" t="n"/>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Cheapest solid</t>
+          <t>Stretch</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>#4 2021 Carbon Edition Turbo · Ron Tonkin Honda</t>
+          <t>#14 2023 2.5 S Premium · Rodland Toyota</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
@@ -3577,93 +3485,56 @@
         </is>
       </c>
       <c r="F26" s="16" t="n">
-        <v>25852</v>
+        <v>28287</v>
       </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="7" t="n"/>
       <c r="I26" s="7" t="n"/>
       <c r="J26" s="7" t="n"/>
       <c r="K26" s="16" t="n">
-        <v>29558.646</v>
+        <v>32028.848</v>
       </c>
       <c r="L26" s="16" t="n">
-        <v>575.5838348034372</v>
+        <v>623.6851023614681</v>
       </c>
       <c r="M26" s="16" t="n">
-        <v>478.2208103260242</v>
+        <v>526.3220778840551</v>
       </c>
       <c r="N26" s="16" t="n">
-        <v>4976.384088206229</v>
+        <v>5392.258141688082</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Stretch</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>#1 2023 2.5 Turbo AWD · Puyallup Mazda</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>est</t>
-        </is>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>27719</v>
-      </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="16" t="n">
-        <v>31512.652</v>
-      </c>
-      <c r="L27" s="16" t="n">
-        <v>613.6334216048396</v>
-      </c>
-      <c r="M27" s="16" t="n">
-        <v>516.2703971274266</v>
-      </c>
-      <c r="N27" s="16" t="n">
-        <v>5305.35329629037</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="25" t="inlineStr">
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>Δ</t>
         </is>
       </c>
-      <c r="D28" s="25" t="n"/>
-      <c r="E28" s="25" t="n"/>
-      <c r="F28" s="26" t="n">
-        <v>1867</v>
-      </c>
-      <c r="G28" s="25" t="n"/>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="25" t="n"/>
-      <c r="J28" s="25" t="n"/>
-      <c r="K28" s="26" t="n">
-        <v>1954.006000000001</v>
-      </c>
-      <c r="L28" s="26" t="n">
-        <v>38.04958680140237</v>
-      </c>
-      <c r="M28" s="26" t="n">
-        <v>38.04958680140243</v>
-      </c>
-      <c r="N28" s="26" t="n">
-        <v>328.9692080841414</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="14" t="inlineStr">
+      <c r="D27" s="25" t="n"/>
+      <c r="E27" s="25" t="n"/>
+      <c r="F27" s="26" t="n">
+        <v>2435</v>
+      </c>
+      <c r="G27" s="25" t="n"/>
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="25" t="n"/>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="26" t="n">
+        <v>2470.202000000001</v>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>48.10126755803094</v>
+      </c>
+      <c r="M27" s="26" t="n">
+        <v>48.101267558031</v>
+      </c>
+      <c r="N27" s="26" t="n">
+        <v>415.8740534818535</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>Rule: cheapest solid = lowest estimated out-the-door figure among live cars with a verified 1-owner / 0-accident history (or Mazda CPO) at a franchise dealer; stretch = best-value live 2023 in the Turbo / Premium tiers, ranked by list price against KBB Seattle fair purchase price.</t>
         </is>
@@ -3681,7 +3552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O9"/>
+  <dimension ref="B1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3.5" customWidth="1" min="1" max="1"/>
@@ -3771,10 +3642,10 @@
     </row>
     <row r="4">
       <c r="B4" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
@@ -3783,63 +3654,63 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Acura of Seattle</t>
+          <t>Puyallup Mazda</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Tukwila, WA</t>
+          <t>Puyallup, WA</t>
         </is>
       </c>
       <c r="G4" s="9" t="n">
-        <v>27300</v>
+        <v>27919</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>25353</v>
+        <v>27990</v>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Aug 11</t>
+          <t>Aug 15</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>confirmed Aug 11 PM</t>
+          <t>purchased by the buyer this report was built for</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/451655500</t>
+          <t>https://www.cargurus.com/Cars/listing/448185375</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Grand Touring Reserve AWD (2.5 Turbo)</t>
+          <t>2.5 Turbo AWD</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>BMW Seattle</t>
+          <t>Acura of Seattle</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Seattle, WA</t>
+          <t>Tukwila, WA</t>
         </is>
       </c>
       <c r="G5" s="9" t="n">
-        <v>24999</v>
+        <v>27300</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>39141</v>
+        <v>25353</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -3848,130 +3719,130 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>dealer confirmed Aug 11 PM; CarGurus copy closed Aug 12</t>
+          <t>confirmed Aug 11 PM</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/455054228</t>
+          <t>https://www.cargurus.com/Cars/listing/451655500</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>2.5 S Preferred AWD</t>
+          <t>Grand Touring Reserve AWD (2.5 Turbo)</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Royal Moore Mazda</t>
+          <t>BMW Seattle</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Hillsboro, OR</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>26900</v>
+        <v>24999</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>16615</v>
+        <v>39141</v>
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Aug 13</t>
+          <t>Aug 11</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>dealer email Aug 13</t>
+          <t>dealer confirmed Aug 11 PM; CarGurus copy closed Aug 12</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>https://www.cargurus.com/Cars/listing/454567468</t>
+          <t>https://www.cargurus.com/Cars/listing/455054228</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Carbon Edition</t>
+          <t>2.5 S Preferred AWD</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>CarMax Sacramento South</t>
+          <t>Royal Moore Mazda</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Hillsboro, OR</t>
         </is>
       </c>
       <c r="G7" s="9" t="n">
-        <v>24998</v>
+        <v>26900</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>48337</v>
+        <v>16615</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Aug 11</t>
+          <t>Aug 13</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Aug 11 PM</t>
+          <t>dealer email Aug 13</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.carmax.com/car/70056694</t>
+          <t>https://www.cargurus.com/Cars/listing/454567468</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Grand Touring AWD</t>
+          <t>Carbon Edition</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Doug's Lynnwood Mazda</t>
+          <t>CarMax Sacramento South</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Edmonds, WA</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="G8" s="9" t="n">
-        <v>28700</v>
+        <v>24998</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>27089</v>
+        <v>48337</v>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
@@ -3980,54 +3851,98 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>dealer email Aug 11 (sold Aug 10)</t>
+          <t>Aug 11 PM</t>
         </is>
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>https://www.cars.com/vehicledetail/495a1e58-37a7-480b-9f80-8bb411d8fa8f/</t>
+          <t>https://www.carmax.com/car/70056694</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>Grand Touring AWD</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Doug's Lynnwood Mazda</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Edmonds, WA</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>28700</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>27089</v>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>Aug 11</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>dealer email Aug 11 (sold Aug 10)</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>https://www.cars.com/vehicledetail/495a1e58-37a7-480b-9f80-8bb411d8fa8f/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C10" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>2.5 S Preferred AWD</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>Auto Connections of Bellevue (independent)</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Bellevue, WA</t>
         </is>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G10" s="9" t="n">
         <v>26495</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="H10" s="6" t="n">
         <v>20533</v>
       </c>
-      <c r="I9" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>Aug 11</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Aug 11, 11:51 AM</t>
         </is>
       </c>
-      <c r="K9" s="7" t="inlineStr">
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>https://www.cargurus.com/Cars/listing/450670232</t>
         </is>
@@ -5489,11 +5404,11 @@
         <v>30980</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>27919</v>
+        <v>28998</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>#1</t>
+          <t>CarGurus</t>
         </is>
       </c>
       <c r="H19" s="16">
@@ -5502,7 +5417,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
